--- a/docs/StudentsAttendance/TheFinalStudentBook.xlsx
+++ b/docs/StudentsAttendance/TheFinalStudentBook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vdc-teacher-app\docs\StudentsAttendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78453E6C-B8D8-465D-BEAD-255F73F53DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6151F241-2B4F-49A9-AEDA-88DDE05085D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="19440" windowHeight="14880" firstSheet="1" activeTab="4" xr2:uid="{D35FEAE2-6E68-4823-87E7-650F27351740}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="19440" windowHeight="14880" firstSheet="2" activeTab="6" xr2:uid="{D35FEAE2-6E68-4823-87E7-650F27351740}"/>
   </bookViews>
   <sheets>
     <sheet name="B.com(2nd year)" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3705" uniqueCount="2242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3841" uniqueCount="2325">
   <si>
     <t>VIVEKANANDA DEGREE COLLGE ADMISSION DETAILS 2024-25 B,COM</t>
   </si>
@@ -6791,6 +6791,255 @@
   </si>
   <si>
     <t>mohan.n1807@gmail.com</t>
+  </si>
+  <si>
+    <t>U18JX26C0115</t>
+  </si>
+  <si>
+    <t>DEEPAK PATEL .T</t>
+  </si>
+  <si>
+    <t>TRILOK PATEL</t>
+  </si>
+  <si>
+    <t>CHAMPA DEVI</t>
+  </si>
+  <si>
+    <t>862111126083</t>
+  </si>
+  <si>
+    <t>537989508367</t>
+  </si>
+  <si>
+    <t>OTHERS</t>
+  </si>
+  <si>
+    <t>KALBI</t>
+  </si>
+  <si>
+    <t>#23/6,4TH CROSS,MAGADI ROAD,BANGALORE-560023.</t>
+  </si>
+  <si>
+    <t>U18JX26C0123</t>
+  </si>
+  <si>
+    <t>RAKESH PATEL</t>
+  </si>
+  <si>
+    <t>CHUTRA RAM</t>
+  </si>
+  <si>
+    <t>DHAPU DEVI</t>
+  </si>
+  <si>
+    <t>274885287500</t>
+  </si>
+  <si>
+    <t>545345460051</t>
+  </si>
+  <si>
+    <t>#149,SULTHANPET MAIN ROAD,BANGALORE-53. / #23/15,4TH CROSS,LEFT SIDE, MAGADI ROAD,BANGALORE-560023.</t>
+  </si>
+  <si>
+    <t>U18JX26C0094</t>
+  </si>
+  <si>
+    <t>BHARGAV .S</t>
+  </si>
+  <si>
+    <t>SANJAY. V</t>
+  </si>
+  <si>
+    <t>ROOPA. S</t>
+  </si>
+  <si>
+    <t>REDDY</t>
+  </si>
+  <si>
+    <t>#10,4THMAIN,NEAR MOURYA SCHOOL,MARUTHI LAYOUT,KAMAKSHIPALYA,BANGALORE-560079.</t>
+  </si>
+  <si>
+    <t>U18JX26C0121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D V.PRUTHVI </t>
+  </si>
+  <si>
+    <t>VENKATESH</t>
+  </si>
+  <si>
+    <t>PUSPAVATHI</t>
+  </si>
+  <si>
+    <t>980930173398</t>
+  </si>
+  <si>
+    <t>375653996535</t>
+  </si>
+  <si>
+    <t>#1ST MAIN ROAD,SRS ROAD,PEENYA 1ST STAGE,BANGALORE-560058.</t>
+  </si>
+  <si>
+    <t>pruthigowda0201@gmail.com</t>
+  </si>
+  <si>
+    <t>U18JX26C</t>
+  </si>
+  <si>
+    <t>TILAK GOWDA.A</t>
+  </si>
+  <si>
+    <t>ANAND.S</t>
+  </si>
+  <si>
+    <t>KUSUMA</t>
+  </si>
+  <si>
+    <t>591913966528</t>
+  </si>
+  <si>
+    <t>987428691901</t>
+  </si>
+  <si>
+    <t>#31,ANUGRAHA ENCLOVE,KADABAGERE,DASANPURA HOBLIE,BANGALORE-562130.</t>
+  </si>
+  <si>
+    <t>tilakgowda@gmail.com</t>
+  </si>
+  <si>
+    <t>U18JX26C0117</t>
+  </si>
+  <si>
+    <t>SNEHA . G</t>
+  </si>
+  <si>
+    <t>GANAPATHI</t>
+  </si>
+  <si>
+    <t>SUMMATHI</t>
+  </si>
+  <si>
+    <t>754137510571</t>
+  </si>
+  <si>
+    <t>800653093913</t>
+  </si>
+  <si>
+    <t>BILLAVA</t>
+  </si>
+  <si>
+    <t>#10TH CROSS,PIPELINE,VIJAYANAGAR,BANGALORE.</t>
+  </si>
+  <si>
+    <t>snehasneha15156@gmail.com</t>
+  </si>
+  <si>
+    <t>U18JX26C0119</t>
+  </si>
+  <si>
+    <t>DEEPA SHREE .R</t>
+  </si>
+  <si>
+    <t>RAMESH. M</t>
+  </si>
+  <si>
+    <t>241992694349</t>
+  </si>
+  <si>
+    <t>467848205284</t>
+  </si>
+  <si>
+    <t>#L1,8TH CROSS,3RD MAIN,L N PURAM,SRIRAMPURA,BANGALORE-560021.</t>
+  </si>
+  <si>
+    <t>mn3637496@gmail.com</t>
+  </si>
+  <si>
+    <t>RADHIKA MASIDDA BASANALA</t>
+  </si>
+  <si>
+    <t>MASIDDA</t>
+  </si>
+  <si>
+    <t>INDRABAYI</t>
+  </si>
+  <si>
+    <t>307869175580</t>
+  </si>
+  <si>
+    <t>343714889367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#2,7TH MAIN ROAD,SHIVANAGARA,RAJAJINAGAR,BANGALORE-560010. </t>
+  </si>
+  <si>
+    <t>radhikabasanala@gmail.com</t>
+  </si>
+  <si>
+    <t>U18JX26C0122</t>
+  </si>
+  <si>
+    <t>JERISH .M</t>
+  </si>
+  <si>
+    <t>MANJUNATH T</t>
+  </si>
+  <si>
+    <t>PRAVEENA</t>
+  </si>
+  <si>
+    <t>780517829891</t>
+  </si>
+  <si>
+    <t>#60,7TH CROSS,7TH MAIN ROAD,RKS NAGAR,SRIRAMPURAM,BANGALORE-560021.</t>
+  </si>
+  <si>
+    <t>nandhusuresh021992@gmail.com</t>
+  </si>
+  <si>
+    <t>U18JX26C0118</t>
+  </si>
+  <si>
+    <t>SATHYA. A</t>
+  </si>
+  <si>
+    <t>APPAJI P</t>
+  </si>
+  <si>
+    <t>SENBAGAM V</t>
+  </si>
+  <si>
+    <t>907209400572</t>
+  </si>
+  <si>
+    <t>580685065526</t>
+  </si>
+  <si>
+    <t>#1ST MAIN CROSS,KANTEERAVA NAGAR,RAMAKRISHNA NAGAR PARK,NANDINI LAYOUT,BANGALORE-560096.</t>
+  </si>
+  <si>
+    <t>U18JX26C0120</t>
+  </si>
+  <si>
+    <t>RAVI. M</t>
+  </si>
+  <si>
+    <t>MUNIYAPPA.T K</t>
+  </si>
+  <si>
+    <t>RATHNA. V</t>
+  </si>
+  <si>
+    <t>704894350712</t>
+  </si>
+  <si>
+    <t>922848149458</t>
+  </si>
+  <si>
+    <t>#KB,2ND ROAD,ANJANNAGAR LAYOUT,BANGALORE-560091.</t>
+  </si>
+  <si>
+    <t>muniyappamuniyappat27@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -7083,12 +7332,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="173">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -7275,6 +7525,14 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -7284,26 +7542,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -7314,34 +7563,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7362,19 +7605,77 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{AFF90935-D1D9-4D0E-8F0D-009F27B250F0}"/>
+    <cellStyle name="Normal 3" xfId="3" xr:uid="{EA3B3A12-251F-4B36-B798-9ACC4133821C}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -7743,45 +8044,45 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:37" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
-      <c r="H1" s="105"/>
-      <c r="I1" s="105"/>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="105"/>
-      <c r="O1" s="105"/>
-      <c r="P1" s="105"/>
-      <c r="Q1" s="105"/>
-      <c r="R1" s="105"/>
-      <c r="S1" s="105"/>
-      <c r="T1" s="105"/>
-      <c r="U1" s="105"/>
-      <c r="V1" s="105"/>
-      <c r="W1" s="105"/>
-      <c r="X1" s="105"/>
-      <c r="Y1" s="105"/>
-      <c r="Z1" s="105"/>
-      <c r="AA1" s="105"/>
-      <c r="AB1" s="105"/>
-      <c r="AC1" s="105"/>
-      <c r="AD1" s="105"/>
-      <c r="AE1" s="105"/>
-      <c r="AF1" s="105"/>
-      <c r="AG1" s="105"/>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="97"/>
+      <c r="I1" s="97"/>
+      <c r="J1" s="97"/>
+      <c r="K1" s="97"/>
+      <c r="L1" s="97"/>
+      <c r="M1" s="97"/>
+      <c r="N1" s="97"/>
+      <c r="O1" s="97"/>
+      <c r="P1" s="97"/>
+      <c r="Q1" s="97"/>
+      <c r="R1" s="97"/>
+      <c r="S1" s="97"/>
+      <c r="T1" s="97"/>
+      <c r="U1" s="97"/>
+      <c r="V1" s="97"/>
+      <c r="W1" s="97"/>
+      <c r="X1" s="97"/>
+      <c r="Y1" s="97"/>
+      <c r="Z1" s="97"/>
+      <c r="AA1" s="97"/>
+      <c r="AB1" s="97"/>
+      <c r="AC1" s="97"/>
+      <c r="AD1" s="97"/>
+      <c r="AE1" s="97"/>
+      <c r="AF1" s="97"/>
+      <c r="AG1" s="97"/>
+      <c r="AH1" s="97"/>
+      <c r="AI1" s="97"/>
+      <c r="AJ1" s="97"/>
+      <c r="AK1" s="97"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -7850,25 +8151,25 @@
       <c r="V2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="W2" s="106" t="s">
+      <c r="W2" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="106"/>
-      <c r="Y2" s="106"/>
-      <c r="Z2" s="106"/>
-      <c r="AA2" s="106"/>
-      <c r="AB2" s="106"/>
-      <c r="AC2" s="106"/>
-      <c r="AD2" s="106"/>
-      <c r="AE2" s="106"/>
-      <c r="AF2" s="98" t="s">
+      <c r="X2" s="98"/>
+      <c r="Y2" s="98"/>
+      <c r="Z2" s="98"/>
+      <c r="AA2" s="98"/>
+      <c r="AB2" s="98"/>
+      <c r="AC2" s="98"/>
+      <c r="AD2" s="98"/>
+      <c r="AE2" s="98"/>
+      <c r="AF2" s="99" t="s">
         <v>24</v>
       </c>
-      <c r="AG2" s="99"/>
-      <c r="AH2" s="99"/>
-      <c r="AI2" s="99"/>
-      <c r="AJ2" s="99"/>
-      <c r="AK2" s="100"/>
+      <c r="AG2" s="100"/>
+      <c r="AH2" s="100"/>
+      <c r="AI2" s="100"/>
+      <c r="AJ2" s="100"/>
+      <c r="AK2" s="101"/>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
@@ -7937,25 +8238,25 @@
       <c r="V3" s="9">
         <v>47428</v>
       </c>
-      <c r="W3" s="88" t="s">
+      <c r="W3" s="92" t="s">
         <v>38</v>
       </c>
-      <c r="X3" s="89"/>
-      <c r="Y3" s="89"/>
-      <c r="Z3" s="89"/>
-      <c r="AA3" s="89"/>
-      <c r="AB3" s="89"/>
-      <c r="AC3" s="89"/>
-      <c r="AD3" s="89"/>
-      <c r="AE3" s="90"/>
-      <c r="AF3" s="109" t="s">
+      <c r="X3" s="93"/>
+      <c r="Y3" s="93"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
+      <c r="AB3" s="93"/>
+      <c r="AC3" s="93"/>
+      <c r="AD3" s="93"/>
+      <c r="AE3" s="94"/>
+      <c r="AF3" s="95" t="s">
         <v>39</v>
       </c>
-      <c r="AG3" s="109"/>
-      <c r="AH3" s="109"/>
-      <c r="AI3" s="109"/>
-      <c r="AJ3" s="109"/>
-      <c r="AK3" s="109"/>
+      <c r="AG3" s="95"/>
+      <c r="AH3" s="95"/>
+      <c r="AI3" s="95"/>
+      <c r="AJ3" s="95"/>
+      <c r="AK3" s="95"/>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
@@ -8022,25 +8323,25 @@
       <c r="V4" s="9">
         <v>47424</v>
       </c>
-      <c r="W4" s="119" t="s">
+      <c r="W4" s="102" t="s">
         <v>50</v>
       </c>
-      <c r="X4" s="89"/>
-      <c r="Y4" s="89"/>
-      <c r="Z4" s="89"/>
-      <c r="AA4" s="89"/>
-      <c r="AB4" s="89"/>
-      <c r="AC4" s="89"/>
-      <c r="AD4" s="89"/>
-      <c r="AE4" s="90"/>
-      <c r="AF4" s="109" t="s">
+      <c r="X4" s="93"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
+      <c r="AB4" s="93"/>
+      <c r="AC4" s="93"/>
+      <c r="AD4" s="93"/>
+      <c r="AE4" s="94"/>
+      <c r="AF4" s="95" t="s">
         <v>51</v>
       </c>
-      <c r="AG4" s="109"/>
-      <c r="AH4" s="109"/>
-      <c r="AI4" s="109"/>
-      <c r="AJ4" s="109"/>
-      <c r="AK4" s="109"/>
+      <c r="AG4" s="95"/>
+      <c r="AH4" s="95"/>
+      <c r="AI4" s="95"/>
+      <c r="AJ4" s="95"/>
+      <c r="AK4" s="95"/>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
@@ -8109,25 +8410,25 @@
       <c r="V5" s="9">
         <v>47431</v>
       </c>
-      <c r="W5" s="88" t="s">
+      <c r="W5" s="92" t="s">
         <v>60</v>
       </c>
-      <c r="X5" s="89"/>
-      <c r="Y5" s="89"/>
-      <c r="Z5" s="89"/>
-      <c r="AA5" s="89"/>
-      <c r="AB5" s="89"/>
-      <c r="AC5" s="89"/>
-      <c r="AD5" s="89"/>
-      <c r="AE5" s="90"/>
-      <c r="AF5" s="109" t="s">
+      <c r="X5" s="93"/>
+      <c r="Y5" s="93"/>
+      <c r="Z5" s="93"/>
+      <c r="AA5" s="93"/>
+      <c r="AB5" s="93"/>
+      <c r="AC5" s="93"/>
+      <c r="AD5" s="93"/>
+      <c r="AE5" s="94"/>
+      <c r="AF5" s="95" t="s">
         <v>61</v>
       </c>
-      <c r="AG5" s="109"/>
-      <c r="AH5" s="109"/>
-      <c r="AI5" s="109"/>
-      <c r="AJ5" s="109"/>
-      <c r="AK5" s="109"/>
+      <c r="AG5" s="95"/>
+      <c r="AH5" s="95"/>
+      <c r="AI5" s="95"/>
+      <c r="AJ5" s="95"/>
+      <c r="AK5" s="95"/>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
@@ -8192,25 +8493,25 @@
       <c r="V6" s="9">
         <v>47432</v>
       </c>
-      <c r="W6" s="88" t="s">
+      <c r="W6" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="X6" s="89"/>
-      <c r="Y6" s="89"/>
-      <c r="Z6" s="89"/>
-      <c r="AA6" s="89"/>
-      <c r="AB6" s="89"/>
-      <c r="AC6" s="89"/>
-      <c r="AD6" s="89"/>
-      <c r="AE6" s="90"/>
-      <c r="AF6" s="109" t="s">
+      <c r="X6" s="93"/>
+      <c r="Y6" s="93"/>
+      <c r="Z6" s="93"/>
+      <c r="AA6" s="93"/>
+      <c r="AB6" s="93"/>
+      <c r="AC6" s="93"/>
+      <c r="AD6" s="93"/>
+      <c r="AE6" s="94"/>
+      <c r="AF6" s="95" t="s">
         <v>71</v>
       </c>
-      <c r="AG6" s="109"/>
-      <c r="AH6" s="109"/>
-      <c r="AI6" s="109"/>
-      <c r="AJ6" s="109"/>
-      <c r="AK6" s="109"/>
+      <c r="AG6" s="95"/>
+      <c r="AH6" s="95"/>
+      <c r="AI6" s="95"/>
+      <c r="AJ6" s="95"/>
+      <c r="AK6" s="95"/>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
@@ -8277,25 +8578,25 @@
       <c r="V7" s="9">
         <v>47430</v>
       </c>
-      <c r="W7" s="88" t="s">
+      <c r="W7" s="92" t="s">
         <v>82</v>
       </c>
-      <c r="X7" s="89"/>
-      <c r="Y7" s="89"/>
-      <c r="Z7" s="89"/>
-      <c r="AA7" s="89"/>
-      <c r="AB7" s="89"/>
-      <c r="AC7" s="89"/>
-      <c r="AD7" s="89"/>
-      <c r="AE7" s="90"/>
-      <c r="AF7" s="109" t="s">
+      <c r="X7" s="93"/>
+      <c r="Y7" s="93"/>
+      <c r="Z7" s="93"/>
+      <c r="AA7" s="93"/>
+      <c r="AB7" s="93"/>
+      <c r="AC7" s="93"/>
+      <c r="AD7" s="93"/>
+      <c r="AE7" s="94"/>
+      <c r="AF7" s="95" t="s">
         <v>83</v>
       </c>
-      <c r="AG7" s="109"/>
-      <c r="AH7" s="109"/>
-      <c r="AI7" s="109"/>
-      <c r="AJ7" s="109"/>
-      <c r="AK7" s="109"/>
+      <c r="AG7" s="95"/>
+      <c r="AH7" s="95"/>
+      <c r="AI7" s="95"/>
+      <c r="AJ7" s="95"/>
+      <c r="AK7" s="95"/>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
@@ -8362,25 +8663,25 @@
       <c r="V8" s="9">
         <v>47447</v>
       </c>
-      <c r="W8" s="88" t="s">
+      <c r="W8" s="92" t="s">
         <v>93</v>
       </c>
-      <c r="X8" s="89"/>
-      <c r="Y8" s="89"/>
-      <c r="Z8" s="89"/>
-      <c r="AA8" s="89"/>
-      <c r="AB8" s="89"/>
-      <c r="AC8" s="89"/>
-      <c r="AD8" s="89"/>
-      <c r="AE8" s="90"/>
-      <c r="AF8" s="109" t="s">
+      <c r="X8" s="93"/>
+      <c r="Y8" s="93"/>
+      <c r="Z8" s="93"/>
+      <c r="AA8" s="93"/>
+      <c r="AB8" s="93"/>
+      <c r="AC8" s="93"/>
+      <c r="AD8" s="93"/>
+      <c r="AE8" s="94"/>
+      <c r="AF8" s="95" t="s">
         <v>94</v>
       </c>
-      <c r="AG8" s="109"/>
-      <c r="AH8" s="109"/>
-      <c r="AI8" s="109"/>
-      <c r="AJ8" s="109"/>
-      <c r="AK8" s="109"/>
+      <c r="AG8" s="95"/>
+      <c r="AH8" s="95"/>
+      <c r="AI8" s="95"/>
+      <c r="AJ8" s="95"/>
+      <c r="AK8" s="95"/>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
@@ -8447,25 +8748,25 @@
       <c r="V9" s="9">
         <v>47441</v>
       </c>
-      <c r="W9" s="88" t="s">
+      <c r="W9" s="92" t="s">
         <v>103</v>
       </c>
-      <c r="X9" s="89"/>
-      <c r="Y9" s="89"/>
-      <c r="Z9" s="89"/>
-      <c r="AA9" s="89"/>
-      <c r="AB9" s="89"/>
-      <c r="AC9" s="89"/>
-      <c r="AD9" s="89"/>
-      <c r="AE9" s="90"/>
-      <c r="AF9" s="109" t="s">
+      <c r="X9" s="93"/>
+      <c r="Y9" s="93"/>
+      <c r="Z9" s="93"/>
+      <c r="AA9" s="93"/>
+      <c r="AB9" s="93"/>
+      <c r="AC9" s="93"/>
+      <c r="AD9" s="93"/>
+      <c r="AE9" s="94"/>
+      <c r="AF9" s="95" t="s">
         <v>104</v>
       </c>
-      <c r="AG9" s="109"/>
-      <c r="AH9" s="109"/>
-      <c r="AI9" s="109"/>
-      <c r="AJ9" s="109"/>
-      <c r="AK9" s="109"/>
+      <c r="AG9" s="95"/>
+      <c r="AH9" s="95"/>
+      <c r="AI9" s="95"/>
+      <c r="AJ9" s="95"/>
+      <c r="AK9" s="95"/>
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
@@ -8532,25 +8833,25 @@
       <c r="V10" s="9">
         <v>47446</v>
       </c>
-      <c r="W10" s="88" t="s">
+      <c r="W10" s="92" t="s">
         <v>112</v>
       </c>
-      <c r="X10" s="89"/>
-      <c r="Y10" s="89"/>
-      <c r="Z10" s="89"/>
-      <c r="AA10" s="89"/>
-      <c r="AB10" s="89"/>
-      <c r="AC10" s="89"/>
-      <c r="AD10" s="89"/>
-      <c r="AE10" s="90"/>
-      <c r="AF10" s="109" t="s">
+      <c r="X10" s="93"/>
+      <c r="Y10" s="93"/>
+      <c r="Z10" s="93"/>
+      <c r="AA10" s="93"/>
+      <c r="AB10" s="93"/>
+      <c r="AC10" s="93"/>
+      <c r="AD10" s="93"/>
+      <c r="AE10" s="94"/>
+      <c r="AF10" s="95" t="s">
         <v>113</v>
       </c>
-      <c r="AG10" s="109"/>
-      <c r="AH10" s="109"/>
-      <c r="AI10" s="109"/>
-      <c r="AJ10" s="109"/>
-      <c r="AK10" s="109"/>
+      <c r="AG10" s="95"/>
+      <c r="AH10" s="95"/>
+      <c r="AI10" s="95"/>
+      <c r="AJ10" s="95"/>
+      <c r="AK10" s="95"/>
     </row>
     <row r="11" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
@@ -8617,25 +8918,25 @@
       <c r="V11" s="9">
         <v>47438</v>
       </c>
-      <c r="W11" s="88" t="s">
+      <c r="W11" s="92" t="s">
         <v>122</v>
       </c>
-      <c r="X11" s="89"/>
-      <c r="Y11" s="89"/>
-      <c r="Z11" s="89"/>
-      <c r="AA11" s="89"/>
-      <c r="AB11" s="89"/>
-      <c r="AC11" s="89"/>
-      <c r="AD11" s="89"/>
-      <c r="AE11" s="90"/>
-      <c r="AF11" s="109" t="s">
+      <c r="X11" s="93"/>
+      <c r="Y11" s="93"/>
+      <c r="Z11" s="93"/>
+      <c r="AA11" s="93"/>
+      <c r="AB11" s="93"/>
+      <c r="AC11" s="93"/>
+      <c r="AD11" s="93"/>
+      <c r="AE11" s="94"/>
+      <c r="AF11" s="95" t="s">
         <v>123</v>
       </c>
-      <c r="AG11" s="91"/>
-      <c r="AH11" s="91"/>
-      <c r="AI11" s="91"/>
-      <c r="AJ11" s="91"/>
-      <c r="AK11" s="91"/>
+      <c r="AG11" s="103"/>
+      <c r="AH11" s="103"/>
+      <c r="AI11" s="103"/>
+      <c r="AJ11" s="103"/>
+      <c r="AK11" s="103"/>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
@@ -8702,25 +9003,25 @@
       <c r="V12" s="9">
         <v>47484</v>
       </c>
-      <c r="W12" s="88" t="s">
+      <c r="W12" s="92" t="s">
         <v>132</v>
       </c>
-      <c r="X12" s="89"/>
-      <c r="Y12" s="89"/>
-      <c r="Z12" s="89"/>
-      <c r="AA12" s="89"/>
-      <c r="AB12" s="89"/>
-      <c r="AC12" s="89"/>
-      <c r="AD12" s="89"/>
-      <c r="AE12" s="90"/>
-      <c r="AF12" s="109" t="s">
+      <c r="X12" s="93"/>
+      <c r="Y12" s="93"/>
+      <c r="Z12" s="93"/>
+      <c r="AA12" s="93"/>
+      <c r="AB12" s="93"/>
+      <c r="AC12" s="93"/>
+      <c r="AD12" s="93"/>
+      <c r="AE12" s="94"/>
+      <c r="AF12" s="95" t="s">
         <v>133</v>
       </c>
-      <c r="AG12" s="91"/>
-      <c r="AH12" s="91"/>
-      <c r="AI12" s="91"/>
-      <c r="AJ12" s="91"/>
-      <c r="AK12" s="91"/>
+      <c r="AG12" s="103"/>
+      <c r="AH12" s="103"/>
+      <c r="AI12" s="103"/>
+      <c r="AJ12" s="103"/>
+      <c r="AK12" s="103"/>
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
@@ -8787,25 +9088,25 @@
       <c r="V13" s="9">
         <v>47495</v>
       </c>
-      <c r="W13" s="88" t="s">
+      <c r="W13" s="92" t="s">
         <v>142</v>
       </c>
-      <c r="X13" s="89"/>
-      <c r="Y13" s="89"/>
-      <c r="Z13" s="89"/>
-      <c r="AA13" s="89"/>
-      <c r="AB13" s="89"/>
-      <c r="AC13" s="89"/>
-      <c r="AD13" s="89"/>
-      <c r="AE13" s="90"/>
-      <c r="AF13" s="109" t="s">
+      <c r="X13" s="93"/>
+      <c r="Y13" s="93"/>
+      <c r="Z13" s="93"/>
+      <c r="AA13" s="93"/>
+      <c r="AB13" s="93"/>
+      <c r="AC13" s="93"/>
+      <c r="AD13" s="93"/>
+      <c r="AE13" s="94"/>
+      <c r="AF13" s="95" t="s">
         <v>143</v>
       </c>
-      <c r="AG13" s="91"/>
-      <c r="AH13" s="91"/>
-      <c r="AI13" s="91"/>
-      <c r="AJ13" s="91"/>
-      <c r="AK13" s="91"/>
+      <c r="AG13" s="103"/>
+      <c r="AH13" s="103"/>
+      <c r="AI13" s="103"/>
+      <c r="AJ13" s="103"/>
+      <c r="AK13" s="103"/>
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
@@ -8872,25 +9173,25 @@
       <c r="V14" s="9">
         <v>47443</v>
       </c>
-      <c r="W14" s="88" t="s">
+      <c r="W14" s="92" t="s">
         <v>151</v>
       </c>
-      <c r="X14" s="89"/>
-      <c r="Y14" s="89"/>
-      <c r="Z14" s="89"/>
-      <c r="AA14" s="89"/>
-      <c r="AB14" s="89"/>
-      <c r="AC14" s="89"/>
-      <c r="AD14" s="89"/>
-      <c r="AE14" s="90"/>
-      <c r="AF14" s="109" t="s">
+      <c r="X14" s="93"/>
+      <c r="Y14" s="93"/>
+      <c r="Z14" s="93"/>
+      <c r="AA14" s="93"/>
+      <c r="AB14" s="93"/>
+      <c r="AC14" s="93"/>
+      <c r="AD14" s="93"/>
+      <c r="AE14" s="94"/>
+      <c r="AF14" s="95" t="s">
         <v>152</v>
       </c>
-      <c r="AG14" s="91"/>
-      <c r="AH14" s="91"/>
-      <c r="AI14" s="91"/>
-      <c r="AJ14" s="91"/>
-      <c r="AK14" s="91"/>
+      <c r="AG14" s="103"/>
+      <c r="AH14" s="103"/>
+      <c r="AI14" s="103"/>
+      <c r="AJ14" s="103"/>
+      <c r="AK14" s="103"/>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
@@ -8957,25 +9258,25 @@
       <c r="V15" s="9">
         <v>47440</v>
       </c>
-      <c r="W15" s="88" t="s">
+      <c r="W15" s="92" t="s">
         <v>160</v>
       </c>
-      <c r="X15" s="89"/>
-      <c r="Y15" s="89"/>
-      <c r="Z15" s="89"/>
-      <c r="AA15" s="89"/>
-      <c r="AB15" s="89"/>
-      <c r="AC15" s="89"/>
-      <c r="AD15" s="89"/>
-      <c r="AE15" s="90"/>
-      <c r="AF15" s="109" t="s">
+      <c r="X15" s="93"/>
+      <c r="Y15" s="93"/>
+      <c r="Z15" s="93"/>
+      <c r="AA15" s="93"/>
+      <c r="AB15" s="93"/>
+      <c r="AC15" s="93"/>
+      <c r="AD15" s="93"/>
+      <c r="AE15" s="94"/>
+      <c r="AF15" s="95" t="s">
         <v>161</v>
       </c>
-      <c r="AG15" s="91"/>
-      <c r="AH15" s="91"/>
-      <c r="AI15" s="91"/>
-      <c r="AJ15" s="91"/>
-      <c r="AK15" s="91"/>
+      <c r="AG15" s="103"/>
+      <c r="AH15" s="103"/>
+      <c r="AI15" s="103"/>
+      <c r="AJ15" s="103"/>
+      <c r="AK15" s="103"/>
     </row>
     <row r="16" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
@@ -9042,25 +9343,25 @@
       <c r="V16" s="9">
         <v>47418</v>
       </c>
-      <c r="W16" s="88" t="s">
+      <c r="W16" s="92" t="s">
         <v>169</v>
       </c>
-      <c r="X16" s="89"/>
-      <c r="Y16" s="89"/>
-      <c r="Z16" s="89"/>
-      <c r="AA16" s="89"/>
-      <c r="AB16" s="89"/>
-      <c r="AC16" s="89"/>
-      <c r="AD16" s="89"/>
-      <c r="AE16" s="90"/>
-      <c r="AF16" s="109" t="s">
+      <c r="X16" s="93"/>
+      <c r="Y16" s="93"/>
+      <c r="Z16" s="93"/>
+      <c r="AA16" s="93"/>
+      <c r="AB16" s="93"/>
+      <c r="AC16" s="93"/>
+      <c r="AD16" s="93"/>
+      <c r="AE16" s="94"/>
+      <c r="AF16" s="95" t="s">
         <v>170</v>
       </c>
-      <c r="AG16" s="91"/>
-      <c r="AH16" s="91"/>
-      <c r="AI16" s="91"/>
-      <c r="AJ16" s="91"/>
-      <c r="AK16" s="91"/>
+      <c r="AG16" s="103"/>
+      <c r="AH16" s="103"/>
+      <c r="AI16" s="103"/>
+      <c r="AJ16" s="103"/>
+      <c r="AK16" s="103"/>
     </row>
     <row r="17" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
@@ -9125,25 +9426,25 @@
       <c r="V17" s="9">
         <v>47413</v>
       </c>
-      <c r="W17" s="88" t="s">
+      <c r="W17" s="92" t="s">
         <v>178</v>
       </c>
-      <c r="X17" s="89"/>
-      <c r="Y17" s="89"/>
-      <c r="Z17" s="89"/>
-      <c r="AA17" s="89"/>
-      <c r="AB17" s="89"/>
-      <c r="AC17" s="89"/>
-      <c r="AD17" s="89"/>
-      <c r="AE17" s="90"/>
-      <c r="AF17" s="109" t="s">
+      <c r="X17" s="93"/>
+      <c r="Y17" s="93"/>
+      <c r="Z17" s="93"/>
+      <c r="AA17" s="93"/>
+      <c r="AB17" s="93"/>
+      <c r="AC17" s="93"/>
+      <c r="AD17" s="93"/>
+      <c r="AE17" s="94"/>
+      <c r="AF17" s="95" t="s">
         <v>179</v>
       </c>
-      <c r="AG17" s="91"/>
-      <c r="AH17" s="91"/>
-      <c r="AI17" s="91"/>
-      <c r="AJ17" s="91"/>
-      <c r="AK17" s="91"/>
+      <c r="AG17" s="103"/>
+      <c r="AH17" s="103"/>
+      <c r="AI17" s="103"/>
+      <c r="AJ17" s="103"/>
+      <c r="AK17" s="103"/>
     </row>
     <row r="18" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
@@ -9210,25 +9511,25 @@
       <c r="V18" s="9">
         <v>47407</v>
       </c>
-      <c r="W18" s="88" t="s">
+      <c r="W18" s="92" t="s">
         <v>188</v>
       </c>
-      <c r="X18" s="89"/>
-      <c r="Y18" s="89"/>
-      <c r="Z18" s="89"/>
-      <c r="AA18" s="89"/>
-      <c r="AB18" s="89"/>
-      <c r="AC18" s="89"/>
-      <c r="AD18" s="89"/>
-      <c r="AE18" s="90"/>
-      <c r="AF18" s="109" t="s">
+      <c r="X18" s="93"/>
+      <c r="Y18" s="93"/>
+      <c r="Z18" s="93"/>
+      <c r="AA18" s="93"/>
+      <c r="AB18" s="93"/>
+      <c r="AC18" s="93"/>
+      <c r="AD18" s="93"/>
+      <c r="AE18" s="94"/>
+      <c r="AF18" s="95" t="s">
         <v>189</v>
       </c>
-      <c r="AG18" s="91"/>
-      <c r="AH18" s="91"/>
-      <c r="AI18" s="91"/>
-      <c r="AJ18" s="91"/>
-      <c r="AK18" s="91"/>
+      <c r="AG18" s="103"/>
+      <c r="AH18" s="103"/>
+      <c r="AI18" s="103"/>
+      <c r="AJ18" s="103"/>
+      <c r="AK18" s="103"/>
     </row>
     <row r="19" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
@@ -9295,25 +9596,25 @@
       <c r="V19" s="9">
         <v>47415</v>
       </c>
-      <c r="W19" s="88" t="s">
+      <c r="W19" s="92" t="s">
         <v>197</v>
       </c>
-      <c r="X19" s="89"/>
-      <c r="Y19" s="89"/>
-      <c r="Z19" s="89"/>
-      <c r="AA19" s="89"/>
-      <c r="AB19" s="89"/>
-      <c r="AC19" s="89"/>
-      <c r="AD19" s="89"/>
-      <c r="AE19" s="90"/>
-      <c r="AF19" s="92" t="s">
+      <c r="X19" s="93"/>
+      <c r="Y19" s="93"/>
+      <c r="Z19" s="93"/>
+      <c r="AA19" s="93"/>
+      <c r="AB19" s="93"/>
+      <c r="AC19" s="93"/>
+      <c r="AD19" s="93"/>
+      <c r="AE19" s="94"/>
+      <c r="AF19" s="104" t="s">
         <v>198</v>
       </c>
-      <c r="AG19" s="89"/>
-      <c r="AH19" s="89"/>
-      <c r="AI19" s="89"/>
-      <c r="AJ19" s="89"/>
-      <c r="AK19" s="90"/>
+      <c r="AG19" s="93"/>
+      <c r="AH19" s="93"/>
+      <c r="AI19" s="93"/>
+      <c r="AJ19" s="93"/>
+      <c r="AK19" s="94"/>
     </row>
     <row r="20" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
@@ -9380,25 +9681,25 @@
       <c r="V20" s="9">
         <v>47410</v>
       </c>
-      <c r="W20" s="88" t="s">
+      <c r="W20" s="92" t="s">
         <v>207</v>
       </c>
-      <c r="X20" s="89"/>
-      <c r="Y20" s="89"/>
-      <c r="Z20" s="89"/>
-      <c r="AA20" s="89"/>
-      <c r="AB20" s="89"/>
-      <c r="AC20" s="89"/>
-      <c r="AD20" s="89"/>
-      <c r="AE20" s="90"/>
-      <c r="AF20" s="109" t="s">
+      <c r="X20" s="93"/>
+      <c r="Y20" s="93"/>
+      <c r="Z20" s="93"/>
+      <c r="AA20" s="93"/>
+      <c r="AB20" s="93"/>
+      <c r="AC20" s="93"/>
+      <c r="AD20" s="93"/>
+      <c r="AE20" s="94"/>
+      <c r="AF20" s="95" t="s">
         <v>208</v>
       </c>
-      <c r="AG20" s="91"/>
-      <c r="AH20" s="91"/>
-      <c r="AI20" s="91"/>
-      <c r="AJ20" s="91"/>
-      <c r="AK20" s="91"/>
+      <c r="AG20" s="103"/>
+      <c r="AH20" s="103"/>
+      <c r="AI20" s="103"/>
+      <c r="AJ20" s="103"/>
+      <c r="AK20" s="103"/>
     </row>
     <row r="21" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
@@ -9463,25 +9764,25 @@
       <c r="V21" s="9">
         <v>47408</v>
       </c>
-      <c r="W21" s="88" t="s">
+      <c r="W21" s="92" t="s">
         <v>215</v>
       </c>
-      <c r="X21" s="89"/>
-      <c r="Y21" s="89"/>
-      <c r="Z21" s="89"/>
-      <c r="AA21" s="89"/>
-      <c r="AB21" s="89"/>
-      <c r="AC21" s="89"/>
-      <c r="AD21" s="89"/>
-      <c r="AE21" s="90"/>
-      <c r="AF21" s="109" t="s">
+      <c r="X21" s="93"/>
+      <c r="Y21" s="93"/>
+      <c r="Z21" s="93"/>
+      <c r="AA21" s="93"/>
+      <c r="AB21" s="93"/>
+      <c r="AC21" s="93"/>
+      <c r="AD21" s="93"/>
+      <c r="AE21" s="94"/>
+      <c r="AF21" s="95" t="s">
         <v>216</v>
       </c>
-      <c r="AG21" s="91"/>
-      <c r="AH21" s="91"/>
-      <c r="AI21" s="91"/>
-      <c r="AJ21" s="91"/>
-      <c r="AK21" s="91"/>
+      <c r="AG21" s="103"/>
+      <c r="AH21" s="103"/>
+      <c r="AI21" s="103"/>
+      <c r="AJ21" s="103"/>
+      <c r="AK21" s="103"/>
     </row>
     <row r="22" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
@@ -10226,25 +10527,25 @@
       <c r="V30" s="9">
         <v>47412</v>
       </c>
-      <c r="W30" s="88" t="s">
+      <c r="W30" s="92" t="s">
         <v>300</v>
       </c>
-      <c r="X30" s="96"/>
-      <c r="Y30" s="96"/>
-      <c r="Z30" s="96"/>
-      <c r="AA30" s="96"/>
-      <c r="AB30" s="96"/>
-      <c r="AC30" s="96"/>
-      <c r="AD30" s="96"/>
-      <c r="AE30" s="97"/>
-      <c r="AF30" s="92" t="s">
+      <c r="X30" s="105"/>
+      <c r="Y30" s="105"/>
+      <c r="Z30" s="105"/>
+      <c r="AA30" s="105"/>
+      <c r="AB30" s="105"/>
+      <c r="AC30" s="105"/>
+      <c r="AD30" s="105"/>
+      <c r="AE30" s="106"/>
+      <c r="AF30" s="104" t="s">
         <v>301</v>
       </c>
-      <c r="AG30" s="89"/>
-      <c r="AH30" s="89"/>
-      <c r="AI30" s="89"/>
-      <c r="AJ30" s="89"/>
-      <c r="AK30" s="90"/>
+      <c r="AG30" s="93"/>
+      <c r="AH30" s="93"/>
+      <c r="AI30" s="93"/>
+      <c r="AJ30" s="93"/>
+      <c r="AK30" s="94"/>
     </row>
     <row r="31" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A31" s="7">
@@ -10311,25 +10612,25 @@
       <c r="V31" s="9">
         <v>47501</v>
       </c>
-      <c r="W31" s="88" t="s">
+      <c r="W31" s="92" t="s">
         <v>309</v>
       </c>
-      <c r="X31" s="89"/>
-      <c r="Y31" s="89"/>
-      <c r="Z31" s="89"/>
-      <c r="AA31" s="89"/>
-      <c r="AB31" s="89"/>
-      <c r="AC31" s="89"/>
-      <c r="AD31" s="89"/>
-      <c r="AE31" s="90"/>
-      <c r="AF31" s="109" t="s">
+      <c r="X31" s="93"/>
+      <c r="Y31" s="93"/>
+      <c r="Z31" s="93"/>
+      <c r="AA31" s="93"/>
+      <c r="AB31" s="93"/>
+      <c r="AC31" s="93"/>
+      <c r="AD31" s="93"/>
+      <c r="AE31" s="94"/>
+      <c r="AF31" s="95" t="s">
         <v>310</v>
       </c>
-      <c r="AG31" s="91"/>
-      <c r="AH31" s="91"/>
-      <c r="AI31" s="91"/>
-      <c r="AJ31" s="91"/>
-      <c r="AK31" s="91"/>
+      <c r="AG31" s="103"/>
+      <c r="AH31" s="103"/>
+      <c r="AI31" s="103"/>
+      <c r="AJ31" s="103"/>
+      <c r="AK31" s="103"/>
     </row>
     <row r="32" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A32" s="7">
@@ -10396,25 +10697,25 @@
       <c r="V32" s="9">
         <v>47414</v>
       </c>
-      <c r="W32" s="88" t="s">
+      <c r="W32" s="92" t="s">
         <v>319</v>
       </c>
-      <c r="X32" s="89"/>
-      <c r="Y32" s="89"/>
-      <c r="Z32" s="89"/>
-      <c r="AA32" s="89"/>
-      <c r="AB32" s="89"/>
-      <c r="AC32" s="89"/>
-      <c r="AD32" s="89"/>
-      <c r="AE32" s="90"/>
-      <c r="AF32" s="109" t="s">
+      <c r="X32" s="93"/>
+      <c r="Y32" s="93"/>
+      <c r="Z32" s="93"/>
+      <c r="AA32" s="93"/>
+      <c r="AB32" s="93"/>
+      <c r="AC32" s="93"/>
+      <c r="AD32" s="93"/>
+      <c r="AE32" s="94"/>
+      <c r="AF32" s="95" t="s">
         <v>320</v>
       </c>
-      <c r="AG32" s="91"/>
-      <c r="AH32" s="91"/>
-      <c r="AI32" s="91"/>
-      <c r="AJ32" s="91"/>
-      <c r="AK32" s="91"/>
+      <c r="AG32" s="103"/>
+      <c r="AH32" s="103"/>
+      <c r="AI32" s="103"/>
+      <c r="AJ32" s="103"/>
+      <c r="AK32" s="103"/>
     </row>
     <row r="33" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A33" s="7">
@@ -10490,14 +10791,14 @@
       <c r="AC33" s="37"/>
       <c r="AD33" s="37"/>
       <c r="AE33" s="11"/>
-      <c r="AF33" s="109" t="s">
+      <c r="AF33" s="95" t="s">
         <v>329</v>
       </c>
-      <c r="AG33" s="91"/>
-      <c r="AH33" s="91"/>
-      <c r="AI33" s="91"/>
-      <c r="AJ33" s="91"/>
-      <c r="AK33" s="91"/>
+      <c r="AG33" s="103"/>
+      <c r="AH33" s="103"/>
+      <c r="AI33" s="103"/>
+      <c r="AJ33" s="103"/>
+      <c r="AK33" s="103"/>
     </row>
     <row r="34" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A34" s="7">
@@ -10564,25 +10865,25 @@
       <c r="V34" s="9">
         <v>47457</v>
       </c>
-      <c r="W34" s="88" t="s">
+      <c r="W34" s="92" t="s">
         <v>338</v>
       </c>
-      <c r="X34" s="89"/>
-      <c r="Y34" s="89"/>
-      <c r="Z34" s="89"/>
-      <c r="AA34" s="89"/>
-      <c r="AB34" s="89"/>
-      <c r="AC34" s="89"/>
-      <c r="AD34" s="89"/>
-      <c r="AE34" s="90"/>
-      <c r="AF34" s="109" t="s">
+      <c r="X34" s="93"/>
+      <c r="Y34" s="93"/>
+      <c r="Z34" s="93"/>
+      <c r="AA34" s="93"/>
+      <c r="AB34" s="93"/>
+      <c r="AC34" s="93"/>
+      <c r="AD34" s="93"/>
+      <c r="AE34" s="94"/>
+      <c r="AF34" s="95" t="s">
         <v>339</v>
       </c>
-      <c r="AG34" s="91"/>
-      <c r="AH34" s="91"/>
-      <c r="AI34" s="91"/>
-      <c r="AJ34" s="91"/>
-      <c r="AK34" s="91"/>
+      <c r="AG34" s="103"/>
+      <c r="AH34" s="103"/>
+      <c r="AI34" s="103"/>
+      <c r="AJ34" s="103"/>
+      <c r="AK34" s="103"/>
     </row>
     <row r="35" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A35" s="7">
@@ -10649,25 +10950,25 @@
       <c r="V35" s="9">
         <v>47470</v>
       </c>
-      <c r="W35" s="88" t="s">
+      <c r="W35" s="92" t="s">
         <v>347</v>
       </c>
-      <c r="X35" s="89"/>
-      <c r="Y35" s="89"/>
-      <c r="Z35" s="89"/>
-      <c r="AA35" s="89"/>
-      <c r="AB35" s="89"/>
-      <c r="AC35" s="89"/>
-      <c r="AD35" s="89"/>
-      <c r="AE35" s="90"/>
-      <c r="AF35" s="109" t="s">
+      <c r="X35" s="93"/>
+      <c r="Y35" s="93"/>
+      <c r="Z35" s="93"/>
+      <c r="AA35" s="93"/>
+      <c r="AB35" s="93"/>
+      <c r="AC35" s="93"/>
+      <c r="AD35" s="93"/>
+      <c r="AE35" s="94"/>
+      <c r="AF35" s="95" t="s">
         <v>348</v>
       </c>
-      <c r="AG35" s="91"/>
-      <c r="AH35" s="91"/>
-      <c r="AI35" s="91"/>
-      <c r="AJ35" s="91"/>
-      <c r="AK35" s="91"/>
+      <c r="AG35" s="103"/>
+      <c r="AH35" s="103"/>
+      <c r="AI35" s="103"/>
+      <c r="AJ35" s="103"/>
+      <c r="AK35" s="103"/>
     </row>
     <row r="36" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A36" s="7">
@@ -10732,25 +11033,25 @@
       <c r="V36" s="22">
         <v>47460</v>
       </c>
-      <c r="W36" s="89" t="s">
+      <c r="W36" s="93" t="s">
         <v>357</v>
       </c>
-      <c r="X36" s="89"/>
-      <c r="Y36" s="89"/>
-      <c r="Z36" s="89"/>
-      <c r="AA36" s="89"/>
-      <c r="AB36" s="89"/>
-      <c r="AC36" s="89"/>
-      <c r="AD36" s="89"/>
-      <c r="AE36" s="90"/>
-      <c r="AF36" s="109" t="s">
+      <c r="X36" s="93"/>
+      <c r="Y36" s="93"/>
+      <c r="Z36" s="93"/>
+      <c r="AA36" s="93"/>
+      <c r="AB36" s="93"/>
+      <c r="AC36" s="93"/>
+      <c r="AD36" s="93"/>
+      <c r="AE36" s="94"/>
+      <c r="AF36" s="95" t="s">
         <v>358</v>
       </c>
-      <c r="AG36" s="91"/>
-      <c r="AH36" s="91"/>
-      <c r="AI36" s="91"/>
-      <c r="AJ36" s="91"/>
-      <c r="AK36" s="91"/>
+      <c r="AG36" s="103"/>
+      <c r="AH36" s="103"/>
+      <c r="AI36" s="103"/>
+      <c r="AJ36" s="103"/>
+      <c r="AK36" s="103"/>
     </row>
     <row r="37" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A37" s="7">
@@ -10817,25 +11118,25 @@
       <c r="V37" s="9">
         <v>47459</v>
       </c>
-      <c r="W37" s="88" t="s">
+      <c r="W37" s="92" t="s">
         <v>367</v>
       </c>
-      <c r="X37" s="89"/>
-      <c r="Y37" s="89"/>
-      <c r="Z37" s="89"/>
-      <c r="AA37" s="89"/>
-      <c r="AB37" s="89"/>
-      <c r="AC37" s="89"/>
-      <c r="AD37" s="89"/>
-      <c r="AE37" s="90"/>
-      <c r="AF37" s="109" t="s">
+      <c r="X37" s="93"/>
+      <c r="Y37" s="93"/>
+      <c r="Z37" s="93"/>
+      <c r="AA37" s="93"/>
+      <c r="AB37" s="93"/>
+      <c r="AC37" s="93"/>
+      <c r="AD37" s="93"/>
+      <c r="AE37" s="94"/>
+      <c r="AF37" s="95" t="s">
         <v>368</v>
       </c>
-      <c r="AG37" s="91"/>
-      <c r="AH37" s="91"/>
-      <c r="AI37" s="91"/>
-      <c r="AJ37" s="91"/>
-      <c r="AK37" s="91"/>
+      <c r="AG37" s="103"/>
+      <c r="AH37" s="103"/>
+      <c r="AI37" s="103"/>
+      <c r="AJ37" s="103"/>
+      <c r="AK37" s="103"/>
     </row>
     <row r="38" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A38" s="7">
@@ -10902,25 +11203,25 @@
       <c r="V38" s="9">
         <v>47448</v>
       </c>
-      <c r="W38" s="88" t="s">
+      <c r="W38" s="92" t="s">
         <v>376</v>
       </c>
-      <c r="X38" s="89"/>
-      <c r="Y38" s="89"/>
-      <c r="Z38" s="89"/>
-      <c r="AA38" s="89"/>
-      <c r="AB38" s="89"/>
-      <c r="AC38" s="89"/>
-      <c r="AD38" s="89"/>
-      <c r="AE38" s="90"/>
-      <c r="AF38" s="109" t="s">
+      <c r="X38" s="93"/>
+      <c r="Y38" s="93"/>
+      <c r="Z38" s="93"/>
+      <c r="AA38" s="93"/>
+      <c r="AB38" s="93"/>
+      <c r="AC38" s="93"/>
+      <c r="AD38" s="93"/>
+      <c r="AE38" s="94"/>
+      <c r="AF38" s="95" t="s">
         <v>377</v>
       </c>
-      <c r="AG38" s="91"/>
-      <c r="AH38" s="91"/>
-      <c r="AI38" s="91"/>
-      <c r="AJ38" s="91"/>
-      <c r="AK38" s="91"/>
+      <c r="AG38" s="103"/>
+      <c r="AH38" s="103"/>
+      <c r="AI38" s="103"/>
+      <c r="AJ38" s="103"/>
+      <c r="AK38" s="103"/>
     </row>
     <row r="39" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A39" s="7">
@@ -10987,25 +11288,25 @@
       <c r="V39" s="9">
         <v>47485</v>
       </c>
-      <c r="W39" s="88" t="s">
+      <c r="W39" s="92" t="s">
         <v>385</v>
       </c>
-      <c r="X39" s="89"/>
-      <c r="Y39" s="89"/>
-      <c r="Z39" s="89"/>
-      <c r="AA39" s="89"/>
-      <c r="AB39" s="89"/>
-      <c r="AC39" s="89"/>
-      <c r="AD39" s="89"/>
-      <c r="AE39" s="90"/>
-      <c r="AF39" s="92" t="s">
+      <c r="X39" s="93"/>
+      <c r="Y39" s="93"/>
+      <c r="Z39" s="93"/>
+      <c r="AA39" s="93"/>
+      <c r="AB39" s="93"/>
+      <c r="AC39" s="93"/>
+      <c r="AD39" s="93"/>
+      <c r="AE39" s="94"/>
+      <c r="AF39" s="104" t="s">
         <v>386</v>
       </c>
-      <c r="AG39" s="89"/>
-      <c r="AH39" s="89"/>
-      <c r="AI39" s="89"/>
-      <c r="AJ39" s="89"/>
-      <c r="AK39" s="90"/>
+      <c r="AG39" s="93"/>
+      <c r="AH39" s="93"/>
+      <c r="AI39" s="93"/>
+      <c r="AJ39" s="93"/>
+      <c r="AK39" s="94"/>
     </row>
     <row r="40" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A40" s="7">
@@ -11072,17 +11373,17 @@
       <c r="V40" s="9">
         <v>47467</v>
       </c>
-      <c r="W40" s="92" t="s">
+      <c r="W40" s="104" t="s">
         <v>394</v>
       </c>
-      <c r="X40" s="93"/>
-      <c r="Y40" s="93"/>
-      <c r="Z40" s="93"/>
-      <c r="AA40" s="93"/>
-      <c r="AB40" s="93"/>
-      <c r="AC40" s="93"/>
-      <c r="AD40" s="93"/>
-      <c r="AE40" s="94"/>
+      <c r="X40" s="107"/>
+      <c r="Y40" s="107"/>
+      <c r="Z40" s="107"/>
+      <c r="AA40" s="107"/>
+      <c r="AB40" s="107"/>
+      <c r="AC40" s="107"/>
+      <c r="AD40" s="107"/>
+      <c r="AE40" s="108"/>
       <c r="AF40" s="30" t="s">
         <v>395</v>
       </c>
@@ -11242,25 +11543,25 @@
       <c r="V42" s="9">
         <v>47492</v>
       </c>
-      <c r="W42" s="88" t="s">
+      <c r="W42" s="92" t="s">
         <v>414</v>
       </c>
-      <c r="X42" s="89"/>
-      <c r="Y42" s="89"/>
-      <c r="Z42" s="89"/>
-      <c r="AA42" s="89"/>
-      <c r="AB42" s="89"/>
-      <c r="AC42" s="89"/>
-      <c r="AD42" s="89"/>
-      <c r="AE42" s="90"/>
-      <c r="AF42" s="88" t="s">
+      <c r="X42" s="93"/>
+      <c r="Y42" s="93"/>
+      <c r="Z42" s="93"/>
+      <c r="AA42" s="93"/>
+      <c r="AB42" s="93"/>
+      <c r="AC42" s="93"/>
+      <c r="AD42" s="93"/>
+      <c r="AE42" s="94"/>
+      <c r="AF42" s="92" t="s">
         <v>415</v>
       </c>
-      <c r="AG42" s="89"/>
-      <c r="AH42" s="89"/>
-      <c r="AI42" s="89"/>
-      <c r="AJ42" s="89"/>
-      <c r="AK42" s="90"/>
+      <c r="AG42" s="93"/>
+      <c r="AH42" s="93"/>
+      <c r="AI42" s="93"/>
+      <c r="AJ42" s="93"/>
+      <c r="AK42" s="94"/>
     </row>
     <row r="43" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A43" s="7">
@@ -11325,17 +11626,17 @@
       <c r="V43" s="9">
         <v>47499</v>
       </c>
-      <c r="W43" s="88" t="s">
+      <c r="W43" s="92" t="s">
         <v>423</v>
       </c>
-      <c r="X43" s="89"/>
-      <c r="Y43" s="89"/>
-      <c r="Z43" s="89"/>
-      <c r="AA43" s="89"/>
-      <c r="AB43" s="89"/>
-      <c r="AC43" s="89"/>
-      <c r="AD43" s="89"/>
-      <c r="AE43" s="90"/>
+      <c r="X43" s="93"/>
+      <c r="Y43" s="93"/>
+      <c r="Z43" s="93"/>
+      <c r="AA43" s="93"/>
+      <c r="AB43" s="93"/>
+      <c r="AC43" s="93"/>
+      <c r="AD43" s="93"/>
+      <c r="AE43" s="94"/>
       <c r="AF43" s="30" t="s">
         <v>424</v>
       </c>
@@ -11410,25 +11711,25 @@
       <c r="V44" s="9">
         <v>47494</v>
       </c>
-      <c r="W44" s="88" t="s">
+      <c r="W44" s="92" t="s">
         <v>433</v>
       </c>
-      <c r="X44" s="89"/>
-      <c r="Y44" s="89"/>
-      <c r="Z44" s="89"/>
-      <c r="AA44" s="89"/>
-      <c r="AB44" s="89"/>
-      <c r="AC44" s="89"/>
-      <c r="AD44" s="89"/>
-      <c r="AE44" s="90"/>
-      <c r="AF44" s="92" t="s">
+      <c r="X44" s="93"/>
+      <c r="Y44" s="93"/>
+      <c r="Z44" s="93"/>
+      <c r="AA44" s="93"/>
+      <c r="AB44" s="93"/>
+      <c r="AC44" s="93"/>
+      <c r="AD44" s="93"/>
+      <c r="AE44" s="94"/>
+      <c r="AF44" s="104" t="s">
         <v>434</v>
       </c>
-      <c r="AG44" s="89"/>
-      <c r="AH44" s="89"/>
-      <c r="AI44" s="89"/>
-      <c r="AJ44" s="89"/>
-      <c r="AK44" s="90"/>
+      <c r="AG44" s="93"/>
+      <c r="AH44" s="93"/>
+      <c r="AI44" s="93"/>
+      <c r="AJ44" s="93"/>
+      <c r="AK44" s="94"/>
     </row>
     <row r="45" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A45" s="7">
@@ -11495,25 +11796,25 @@
       <c r="V45" s="9">
         <v>47442</v>
       </c>
-      <c r="W45" s="88" t="s">
+      <c r="W45" s="92" t="s">
         <v>442</v>
       </c>
-      <c r="X45" s="89"/>
-      <c r="Y45" s="89"/>
-      <c r="Z45" s="89"/>
-      <c r="AA45" s="89"/>
-      <c r="AB45" s="89"/>
-      <c r="AC45" s="89"/>
-      <c r="AD45" s="89"/>
-      <c r="AE45" s="90"/>
-      <c r="AF45" s="92" t="s">
+      <c r="X45" s="93"/>
+      <c r="Y45" s="93"/>
+      <c r="Z45" s="93"/>
+      <c r="AA45" s="93"/>
+      <c r="AB45" s="93"/>
+      <c r="AC45" s="93"/>
+      <c r="AD45" s="93"/>
+      <c r="AE45" s="94"/>
+      <c r="AF45" s="104" t="s">
         <v>443</v>
       </c>
-      <c r="AG45" s="89"/>
-      <c r="AH45" s="89"/>
-      <c r="AI45" s="89"/>
-      <c r="AJ45" s="89"/>
-      <c r="AK45" s="90"/>
+      <c r="AG45" s="93"/>
+      <c r="AH45" s="93"/>
+      <c r="AI45" s="93"/>
+      <c r="AJ45" s="93"/>
+      <c r="AK45" s="94"/>
     </row>
     <row r="46" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A46" s="7">
@@ -11580,25 +11881,25 @@
       <c r="V46" s="9">
         <v>47471</v>
       </c>
-      <c r="W46" s="116" t="s">
+      <c r="W46" s="113" t="s">
         <v>452</v>
       </c>
-      <c r="X46" s="117"/>
-      <c r="Y46" s="117"/>
-      <c r="Z46" s="117"/>
-      <c r="AA46" s="117"/>
-      <c r="AB46" s="117"/>
-      <c r="AC46" s="117"/>
-      <c r="AD46" s="117"/>
-      <c r="AE46" s="118"/>
-      <c r="AF46" s="92" t="s">
+      <c r="X46" s="114"/>
+      <c r="Y46" s="114"/>
+      <c r="Z46" s="114"/>
+      <c r="AA46" s="114"/>
+      <c r="AB46" s="114"/>
+      <c r="AC46" s="114"/>
+      <c r="AD46" s="114"/>
+      <c r="AE46" s="115"/>
+      <c r="AF46" s="104" t="s">
         <v>453</v>
       </c>
-      <c r="AG46" s="89"/>
-      <c r="AH46" s="89"/>
-      <c r="AI46" s="89"/>
-      <c r="AJ46" s="89"/>
-      <c r="AK46" s="90"/>
+      <c r="AG46" s="93"/>
+      <c r="AH46" s="93"/>
+      <c r="AI46" s="93"/>
+      <c r="AJ46" s="93"/>
+      <c r="AK46" s="94"/>
     </row>
     <row r="47" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A47" s="7">
@@ -11665,25 +11966,25 @@
       <c r="V47" s="9">
         <v>47450</v>
       </c>
-      <c r="W47" s="95" t="s">
+      <c r="W47" s="109" t="s">
         <v>461</v>
       </c>
-      <c r="X47" s="96"/>
-      <c r="Y47" s="96"/>
-      <c r="Z47" s="96"/>
-      <c r="AA47" s="96"/>
-      <c r="AB47" s="96"/>
-      <c r="AC47" s="96"/>
-      <c r="AD47" s="96"/>
-      <c r="AE47" s="97"/>
-      <c r="AF47" s="92" t="s">
+      <c r="X47" s="105"/>
+      <c r="Y47" s="105"/>
+      <c r="Z47" s="105"/>
+      <c r="AA47" s="105"/>
+      <c r="AB47" s="105"/>
+      <c r="AC47" s="105"/>
+      <c r="AD47" s="105"/>
+      <c r="AE47" s="106"/>
+      <c r="AF47" s="104" t="s">
         <v>462</v>
       </c>
-      <c r="AG47" s="89"/>
-      <c r="AH47" s="89"/>
-      <c r="AI47" s="89"/>
-      <c r="AJ47" s="89"/>
-      <c r="AK47" s="90"/>
+      <c r="AG47" s="93"/>
+      <c r="AH47" s="93"/>
+      <c r="AI47" s="93"/>
+      <c r="AJ47" s="93"/>
+      <c r="AK47" s="94"/>
     </row>
     <row r="48" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="7">
@@ -11750,25 +12051,25 @@
       <c r="V48" s="9">
         <v>47452</v>
       </c>
-      <c r="W48" s="113" t="s">
+      <c r="W48" s="110" t="s">
         <v>471</v>
       </c>
-      <c r="X48" s="114"/>
-      <c r="Y48" s="114"/>
-      <c r="Z48" s="114"/>
-      <c r="AA48" s="114"/>
-      <c r="AB48" s="114"/>
-      <c r="AC48" s="114"/>
-      <c r="AD48" s="114"/>
-      <c r="AE48" s="115"/>
-      <c r="AF48" s="92" t="s">
+      <c r="X48" s="111"/>
+      <c r="Y48" s="111"/>
+      <c r="Z48" s="111"/>
+      <c r="AA48" s="111"/>
+      <c r="AB48" s="111"/>
+      <c r="AC48" s="111"/>
+      <c r="AD48" s="111"/>
+      <c r="AE48" s="112"/>
+      <c r="AF48" s="104" t="s">
         <v>472</v>
       </c>
-      <c r="AG48" s="89"/>
-      <c r="AH48" s="89"/>
-      <c r="AI48" s="89"/>
-      <c r="AJ48" s="89"/>
-      <c r="AK48" s="90"/>
+      <c r="AG48" s="93"/>
+      <c r="AH48" s="93"/>
+      <c r="AI48" s="93"/>
+      <c r="AJ48" s="93"/>
+      <c r="AK48" s="94"/>
     </row>
     <row r="49" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A49" s="7">
@@ -11835,25 +12136,25 @@
       <c r="V49" s="9">
         <v>47462</v>
       </c>
-      <c r="W49" s="88" t="s">
+      <c r="W49" s="92" t="s">
         <v>480</v>
       </c>
-      <c r="X49" s="89"/>
-      <c r="Y49" s="89"/>
-      <c r="Z49" s="89"/>
-      <c r="AA49" s="89"/>
-      <c r="AB49" s="89"/>
-      <c r="AC49" s="89"/>
-      <c r="AD49" s="89"/>
-      <c r="AE49" s="90"/>
-      <c r="AF49" s="92" t="s">
+      <c r="X49" s="93"/>
+      <c r="Y49" s="93"/>
+      <c r="Z49" s="93"/>
+      <c r="AA49" s="93"/>
+      <c r="AB49" s="93"/>
+      <c r="AC49" s="93"/>
+      <c r="AD49" s="93"/>
+      <c r="AE49" s="94"/>
+      <c r="AF49" s="104" t="s">
         <v>481</v>
       </c>
-      <c r="AG49" s="89"/>
-      <c r="AH49" s="89"/>
-      <c r="AI49" s="89"/>
-      <c r="AJ49" s="89"/>
-      <c r="AK49" s="90"/>
+      <c r="AG49" s="93"/>
+      <c r="AH49" s="93"/>
+      <c r="AI49" s="93"/>
+      <c r="AJ49" s="93"/>
+      <c r="AK49" s="94"/>
     </row>
     <row r="50" spans="1:37" ht="18" x14ac:dyDescent="0.35">
       <c r="A50" s="7">
@@ -11920,17 +12221,17 @@
       <c r="V50" s="9">
         <v>47496</v>
       </c>
-      <c r="W50" s="88" t="s">
+      <c r="W50" s="92" t="s">
         <v>490</v>
       </c>
-      <c r="X50" s="89"/>
-      <c r="Y50" s="89"/>
-      <c r="Z50" s="89"/>
-      <c r="AA50" s="89"/>
-      <c r="AB50" s="89"/>
-      <c r="AC50" s="89"/>
-      <c r="AD50" s="89"/>
-      <c r="AE50" s="90"/>
+      <c r="X50" s="93"/>
+      <c r="Y50" s="93"/>
+      <c r="Z50" s="93"/>
+      <c r="AA50" s="93"/>
+      <c r="AB50" s="93"/>
+      <c r="AC50" s="93"/>
+      <c r="AD50" s="93"/>
+      <c r="AE50" s="94"/>
       <c r="AF50" s="30" t="s">
         <v>491</v>
       </c>
@@ -12088,17 +12389,17 @@
       <c r="V52" s="9">
         <v>47514</v>
       </c>
-      <c r="W52" s="88" t="s">
+      <c r="W52" s="92" t="s">
         <v>508</v>
       </c>
-      <c r="X52" s="89"/>
-      <c r="Y52" s="89"/>
-      <c r="Z52" s="89"/>
-      <c r="AA52" s="89"/>
-      <c r="AB52" s="89"/>
-      <c r="AC52" s="89"/>
-      <c r="AD52" s="89"/>
-      <c r="AE52" s="90"/>
+      <c r="X52" s="93"/>
+      <c r="Y52" s="93"/>
+      <c r="Z52" s="93"/>
+      <c r="AA52" s="93"/>
+      <c r="AB52" s="93"/>
+      <c r="AC52" s="93"/>
+      <c r="AD52" s="93"/>
+      <c r="AE52" s="94"/>
       <c r="AF52" s="30" t="s">
         <v>509</v>
       </c>
@@ -12258,17 +12559,17 @@
       <c r="V54" s="9">
         <v>47437</v>
       </c>
-      <c r="W54" s="88" t="s">
+      <c r="W54" s="92" t="s">
         <v>526</v>
       </c>
-      <c r="X54" s="89"/>
-      <c r="Y54" s="89"/>
-      <c r="Z54" s="89"/>
-      <c r="AA54" s="89"/>
-      <c r="AB54" s="89"/>
-      <c r="AC54" s="89"/>
-      <c r="AD54" s="89"/>
-      <c r="AE54" s="90"/>
+      <c r="X54" s="93"/>
+      <c r="Y54" s="93"/>
+      <c r="Z54" s="93"/>
+      <c r="AA54" s="93"/>
+      <c r="AB54" s="93"/>
+      <c r="AC54" s="93"/>
+      <c r="AD54" s="93"/>
+      <c r="AE54" s="94"/>
       <c r="AF54" s="30"/>
       <c r="AG54" s="16"/>
       <c r="AH54" s="16"/>
@@ -12341,25 +12642,25 @@
       <c r="V55" s="9">
         <v>47427</v>
       </c>
-      <c r="W55" s="88" t="s">
+      <c r="W55" s="92" t="s">
         <v>534</v>
       </c>
-      <c r="X55" s="89"/>
-      <c r="Y55" s="89"/>
-      <c r="Z55" s="89"/>
-      <c r="AA55" s="89"/>
-      <c r="AB55" s="89"/>
-      <c r="AC55" s="89"/>
-      <c r="AD55" s="89"/>
-      <c r="AE55" s="90"/>
-      <c r="AF55" s="92" t="s">
+      <c r="X55" s="93"/>
+      <c r="Y55" s="93"/>
+      <c r="Z55" s="93"/>
+      <c r="AA55" s="93"/>
+      <c r="AB55" s="93"/>
+      <c r="AC55" s="93"/>
+      <c r="AD55" s="93"/>
+      <c r="AE55" s="94"/>
+      <c r="AF55" s="104" t="s">
         <v>535</v>
       </c>
-      <c r="AG55" s="89"/>
-      <c r="AH55" s="89"/>
-      <c r="AI55" s="89"/>
-      <c r="AJ55" s="89"/>
-      <c r="AK55" s="90"/>
+      <c r="AG55" s="93"/>
+      <c r="AH55" s="93"/>
+      <c r="AI55" s="93"/>
+      <c r="AJ55" s="93"/>
+      <c r="AK55" s="94"/>
     </row>
     <row r="56" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A56" s="7">
@@ -12426,25 +12727,25 @@
       <c r="V56" s="9">
         <v>47490</v>
       </c>
-      <c r="W56" s="88" t="s">
+      <c r="W56" s="92" t="s">
         <v>545</v>
       </c>
-      <c r="X56" s="96"/>
-      <c r="Y56" s="96"/>
-      <c r="Z56" s="96"/>
-      <c r="AA56" s="96"/>
-      <c r="AB56" s="96"/>
-      <c r="AC56" s="96"/>
-      <c r="AD56" s="96"/>
-      <c r="AE56" s="97"/>
-      <c r="AF56" s="92" t="s">
+      <c r="X56" s="105"/>
+      <c r="Y56" s="105"/>
+      <c r="Z56" s="105"/>
+      <c r="AA56" s="105"/>
+      <c r="AB56" s="105"/>
+      <c r="AC56" s="105"/>
+      <c r="AD56" s="105"/>
+      <c r="AE56" s="106"/>
+      <c r="AF56" s="104" t="s">
         <v>546</v>
       </c>
-      <c r="AG56" s="89"/>
-      <c r="AH56" s="89"/>
-      <c r="AI56" s="89"/>
-      <c r="AJ56" s="89"/>
-      <c r="AK56" s="90"/>
+      <c r="AG56" s="93"/>
+      <c r="AH56" s="93"/>
+      <c r="AI56" s="93"/>
+      <c r="AJ56" s="93"/>
+      <c r="AK56" s="94"/>
     </row>
     <row r="57" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A57" s="7">
@@ -12511,23 +12812,23 @@
       <c r="V57" s="9">
         <v>47444</v>
       </c>
-      <c r="W57" s="88" t="s">
+      <c r="W57" s="92" t="s">
         <v>555</v>
       </c>
-      <c r="X57" s="89"/>
-      <c r="Y57" s="89"/>
-      <c r="Z57" s="89"/>
-      <c r="AA57" s="89"/>
-      <c r="AB57" s="89"/>
-      <c r="AC57" s="89"/>
-      <c r="AD57" s="89"/>
-      <c r="AE57" s="90"/>
-      <c r="AF57" s="92"/>
-      <c r="AG57" s="89"/>
-      <c r="AH57" s="89"/>
-      <c r="AI57" s="89"/>
-      <c r="AJ57" s="89"/>
-      <c r="AK57" s="90"/>
+      <c r="X57" s="93"/>
+      <c r="Y57" s="93"/>
+      <c r="Z57" s="93"/>
+      <c r="AA57" s="93"/>
+      <c r="AB57" s="93"/>
+      <c r="AC57" s="93"/>
+      <c r="AD57" s="93"/>
+      <c r="AE57" s="94"/>
+      <c r="AF57" s="104"/>
+      <c r="AG57" s="93"/>
+      <c r="AH57" s="93"/>
+      <c r="AI57" s="93"/>
+      <c r="AJ57" s="93"/>
+      <c r="AK57" s="94"/>
     </row>
     <row r="58" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A58" s="7">
@@ -12594,25 +12895,25 @@
       <c r="V58" s="9">
         <v>47436</v>
       </c>
-      <c r="W58" s="88" t="s">
+      <c r="W58" s="92" t="s">
         <v>564</v>
       </c>
-      <c r="X58" s="89"/>
-      <c r="Y58" s="89"/>
-      <c r="Z58" s="89"/>
-      <c r="AA58" s="89"/>
-      <c r="AB58" s="89"/>
-      <c r="AC58" s="89"/>
-      <c r="AD58" s="89"/>
-      <c r="AE58" s="90"/>
-      <c r="AF58" s="92" t="s">
+      <c r="X58" s="93"/>
+      <c r="Y58" s="93"/>
+      <c r="Z58" s="93"/>
+      <c r="AA58" s="93"/>
+      <c r="AB58" s="93"/>
+      <c r="AC58" s="93"/>
+      <c r="AD58" s="93"/>
+      <c r="AE58" s="94"/>
+      <c r="AF58" s="104" t="s">
         <v>565</v>
       </c>
-      <c r="AG58" s="89"/>
-      <c r="AH58" s="89"/>
-      <c r="AI58" s="89"/>
-      <c r="AJ58" s="89"/>
-      <c r="AK58" s="90"/>
+      <c r="AG58" s="93"/>
+      <c r="AH58" s="93"/>
+      <c r="AI58" s="93"/>
+      <c r="AJ58" s="93"/>
+      <c r="AK58" s="94"/>
     </row>
     <row r="59" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A59" s="7">
@@ -12849,25 +13150,25 @@
       <c r="V61" s="9">
         <v>47343</v>
       </c>
-      <c r="W61" s="88" t="s">
+      <c r="W61" s="92" t="s">
         <v>591</v>
       </c>
-      <c r="X61" s="89"/>
-      <c r="Y61" s="89"/>
-      <c r="Z61" s="89"/>
-      <c r="AA61" s="89"/>
-      <c r="AB61" s="89"/>
-      <c r="AC61" s="89"/>
-      <c r="AD61" s="89"/>
-      <c r="AE61" s="90"/>
-      <c r="AF61" s="110" t="s">
+      <c r="X61" s="93"/>
+      <c r="Y61" s="93"/>
+      <c r="Z61" s="93"/>
+      <c r="AA61" s="93"/>
+      <c r="AB61" s="93"/>
+      <c r="AC61" s="93"/>
+      <c r="AD61" s="93"/>
+      <c r="AE61" s="94"/>
+      <c r="AF61" s="116" t="s">
         <v>592</v>
       </c>
-      <c r="AG61" s="111"/>
-      <c r="AH61" s="111"/>
-      <c r="AI61" s="111"/>
-      <c r="AJ61" s="111"/>
-      <c r="AK61" s="112"/>
+      <c r="AG61" s="117"/>
+      <c r="AH61" s="117"/>
+      <c r="AI61" s="117"/>
+      <c r="AJ61" s="117"/>
+      <c r="AK61" s="118"/>
     </row>
     <row r="62" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A62" s="7">
@@ -12934,25 +13235,25 @@
       <c r="V62" s="7">
         <v>47429</v>
       </c>
-      <c r="W62" s="88" t="s">
+      <c r="W62" s="92" t="s">
         <v>601</v>
       </c>
-      <c r="X62" s="89"/>
-      <c r="Y62" s="89"/>
-      <c r="Z62" s="89"/>
-      <c r="AA62" s="89"/>
-      <c r="AB62" s="89"/>
-      <c r="AC62" s="89"/>
-      <c r="AD62" s="89"/>
-      <c r="AE62" s="90"/>
-      <c r="AF62" s="109" t="s">
+      <c r="X62" s="93"/>
+      <c r="Y62" s="93"/>
+      <c r="Z62" s="93"/>
+      <c r="AA62" s="93"/>
+      <c r="AB62" s="93"/>
+      <c r="AC62" s="93"/>
+      <c r="AD62" s="93"/>
+      <c r="AE62" s="94"/>
+      <c r="AF62" s="95" t="s">
         <v>602</v>
       </c>
-      <c r="AG62" s="91"/>
-      <c r="AH62" s="91"/>
-      <c r="AI62" s="91"/>
-      <c r="AJ62" s="91"/>
-      <c r="AK62" s="91"/>
+      <c r="AG62" s="103"/>
+      <c r="AH62" s="103"/>
+      <c r="AI62" s="103"/>
+      <c r="AJ62" s="103"/>
+      <c r="AK62" s="103"/>
     </row>
     <row r="63" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A63" s="7">
@@ -13017,25 +13318,25 @@
       <c r="V63" s="9">
         <v>47449</v>
       </c>
-      <c r="W63" s="88" t="s">
+      <c r="W63" s="92" t="s">
         <v>609</v>
       </c>
-      <c r="X63" s="89"/>
-      <c r="Y63" s="89"/>
-      <c r="Z63" s="89"/>
-      <c r="AA63" s="89"/>
-      <c r="AB63" s="89"/>
-      <c r="AC63" s="89"/>
-      <c r="AD63" s="89"/>
-      <c r="AE63" s="90"/>
-      <c r="AF63" s="92" t="s">
+      <c r="X63" s="93"/>
+      <c r="Y63" s="93"/>
+      <c r="Z63" s="93"/>
+      <c r="AA63" s="93"/>
+      <c r="AB63" s="93"/>
+      <c r="AC63" s="93"/>
+      <c r="AD63" s="93"/>
+      <c r="AE63" s="94"/>
+      <c r="AF63" s="104" t="s">
         <v>610</v>
       </c>
-      <c r="AG63" s="89"/>
-      <c r="AH63" s="89"/>
-      <c r="AI63" s="89"/>
-      <c r="AJ63" s="89"/>
-      <c r="AK63" s="90"/>
+      <c r="AG63" s="93"/>
+      <c r="AH63" s="93"/>
+      <c r="AI63" s="93"/>
+      <c r="AJ63" s="93"/>
+      <c r="AK63" s="94"/>
     </row>
     <row r="64" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="7">
@@ -13102,17 +13403,17 @@
       <c r="V64" s="9">
         <v>47458</v>
       </c>
-      <c r="W64" s="88" t="s">
+      <c r="W64" s="92" t="s">
         <v>618</v>
       </c>
-      <c r="X64" s="89"/>
-      <c r="Y64" s="89"/>
-      <c r="Z64" s="89"/>
-      <c r="AA64" s="89"/>
-      <c r="AB64" s="89"/>
-      <c r="AC64" s="89"/>
-      <c r="AD64" s="89"/>
-      <c r="AE64" s="90"/>
+      <c r="X64" s="93"/>
+      <c r="Y64" s="93"/>
+      <c r="Z64" s="93"/>
+      <c r="AA64" s="93"/>
+      <c r="AB64" s="93"/>
+      <c r="AC64" s="93"/>
+      <c r="AD64" s="93"/>
+      <c r="AE64" s="94"/>
       <c r="AF64" s="30" t="s">
         <v>619</v>
       </c>
@@ -13185,17 +13486,17 @@
       <c r="V65" s="9">
         <v>47445</v>
       </c>
-      <c r="W65" s="88" t="s">
+      <c r="W65" s="92" t="s">
         <v>625</v>
       </c>
-      <c r="X65" s="89"/>
-      <c r="Y65" s="89"/>
-      <c r="Z65" s="89"/>
-      <c r="AA65" s="89"/>
-      <c r="AB65" s="89"/>
-      <c r="AC65" s="89"/>
-      <c r="AD65" s="89"/>
-      <c r="AE65" s="90"/>
+      <c r="X65" s="93"/>
+      <c r="Y65" s="93"/>
+      <c r="Z65" s="93"/>
+      <c r="AA65" s="93"/>
+      <c r="AB65" s="93"/>
+      <c r="AC65" s="93"/>
+      <c r="AD65" s="93"/>
+      <c r="AE65" s="94"/>
       <c r="AF65" s="30" t="s">
         <v>626</v>
       </c>
@@ -13355,28 +13656,28 @@
       <c r="V67" s="9">
         <v>47519</v>
       </c>
-      <c r="W67" s="108" t="s">
+      <c r="W67" s="119" t="s">
         <v>645</v>
       </c>
-      <c r="X67" s="89"/>
-      <c r="Y67" s="89"/>
-      <c r="Z67" s="89"/>
-      <c r="AA67" s="89"/>
-      <c r="AB67" s="89"/>
-      <c r="AC67" s="89"/>
-      <c r="AD67" s="89"/>
-      <c r="AE67" s="90"/>
-      <c r="AF67" s="92" t="s">
+      <c r="X67" s="93"/>
+      <c r="Y67" s="93"/>
+      <c r="Z67" s="93"/>
+      <c r="AA67" s="93"/>
+      <c r="AB67" s="93"/>
+      <c r="AC67" s="93"/>
+      <c r="AD67" s="93"/>
+      <c r="AE67" s="94"/>
+      <c r="AF67" s="104" t="s">
         <v>646</v>
       </c>
-      <c r="AG67" s="89"/>
-      <c r="AH67" s="89"/>
-      <c r="AI67" s="89"/>
-      <c r="AJ67" s="89"/>
-      <c r="AK67" s="89"/>
-      <c r="AL67" s="89"/>
-      <c r="AM67" s="89"/>
-      <c r="AN67" s="90"/>
+      <c r="AG67" s="93"/>
+      <c r="AH67" s="93"/>
+      <c r="AI67" s="93"/>
+      <c r="AJ67" s="93"/>
+      <c r="AK67" s="93"/>
+      <c r="AL67" s="93"/>
+      <c r="AM67" s="93"/>
+      <c r="AN67" s="94"/>
     </row>
     <row r="68" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A68" s="7">
@@ -13443,28 +13744,28 @@
       <c r="V68" s="9">
         <v>47468</v>
       </c>
-      <c r="W68" s="92" t="s">
+      <c r="W68" s="104" t="s">
         <v>654</v>
       </c>
-      <c r="X68" s="89"/>
-      <c r="Y68" s="89"/>
-      <c r="Z68" s="89"/>
-      <c r="AA68" s="89"/>
-      <c r="AB68" s="89"/>
-      <c r="AC68" s="89"/>
-      <c r="AD68" s="89"/>
-      <c r="AE68" s="90"/>
-      <c r="AF68" s="92" t="s">
+      <c r="X68" s="93"/>
+      <c r="Y68" s="93"/>
+      <c r="Z68" s="93"/>
+      <c r="AA68" s="93"/>
+      <c r="AB68" s="93"/>
+      <c r="AC68" s="93"/>
+      <c r="AD68" s="93"/>
+      <c r="AE68" s="94"/>
+      <c r="AF68" s="104" t="s">
         <v>655</v>
       </c>
-      <c r="AG68" s="89"/>
-      <c r="AH68" s="89"/>
-      <c r="AI68" s="89"/>
-      <c r="AJ68" s="89"/>
-      <c r="AK68" s="89"/>
-      <c r="AL68" s="89"/>
-      <c r="AM68" s="89"/>
-      <c r="AN68" s="90"/>
+      <c r="AG68" s="93"/>
+      <c r="AH68" s="93"/>
+      <c r="AI68" s="93"/>
+      <c r="AJ68" s="93"/>
+      <c r="AK68" s="93"/>
+      <c r="AL68" s="93"/>
+      <c r="AM68" s="93"/>
+      <c r="AN68" s="94"/>
     </row>
     <row r="69" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A69" s="7">
@@ -13531,17 +13832,17 @@
       <c r="V69" s="9">
         <v>47467</v>
       </c>
-      <c r="W69" s="88" t="s">
+      <c r="W69" s="92" t="s">
         <v>663</v>
       </c>
-      <c r="X69" s="89"/>
-      <c r="Y69" s="89"/>
-      <c r="Z69" s="89"/>
-      <c r="AA69" s="89"/>
-      <c r="AB69" s="89"/>
-      <c r="AC69" s="89"/>
-      <c r="AD69" s="89"/>
-      <c r="AE69" s="90"/>
+      <c r="X69" s="93"/>
+      <c r="Y69" s="93"/>
+      <c r="Z69" s="93"/>
+      <c r="AA69" s="93"/>
+      <c r="AB69" s="93"/>
+      <c r="AC69" s="93"/>
+      <c r="AD69" s="93"/>
+      <c r="AE69" s="94"/>
       <c r="AF69" s="30" t="s">
         <v>664</v>
       </c>
@@ -13616,23 +13917,23 @@
       <c r="V70" s="9">
         <v>47435</v>
       </c>
-      <c r="W70" s="88" t="s">
+      <c r="W70" s="92" t="s">
         <v>672</v>
       </c>
-      <c r="X70" s="89"/>
-      <c r="Y70" s="89"/>
-      <c r="Z70" s="89"/>
-      <c r="AA70" s="89"/>
-      <c r="AB70" s="89"/>
-      <c r="AC70" s="89"/>
-      <c r="AD70" s="89"/>
-      <c r="AE70" s="90"/>
-      <c r="AF70" s="92" t="s">
+      <c r="X70" s="93"/>
+      <c r="Y70" s="93"/>
+      <c r="Z70" s="93"/>
+      <c r="AA70" s="93"/>
+      <c r="AB70" s="93"/>
+      <c r="AC70" s="93"/>
+      <c r="AD70" s="93"/>
+      <c r="AE70" s="94"/>
+      <c r="AF70" s="104" t="s">
         <v>673</v>
       </c>
-      <c r="AG70" s="93"/>
-      <c r="AH70" s="93"/>
-      <c r="AI70" s="93"/>
+      <c r="AG70" s="107"/>
+      <c r="AH70" s="107"/>
+      <c r="AI70" s="107"/>
       <c r="AJ70" s="16"/>
       <c r="AK70" s="17"/>
     </row>
@@ -13699,17 +14000,17 @@
       <c r="V71" s="9">
         <v>47463</v>
       </c>
-      <c r="W71" s="88" t="s">
+      <c r="W71" s="92" t="s">
         <v>681</v>
       </c>
-      <c r="X71" s="89"/>
-      <c r="Y71" s="89"/>
-      <c r="Z71" s="89"/>
-      <c r="AA71" s="89"/>
-      <c r="AB71" s="89"/>
-      <c r="AC71" s="89"/>
-      <c r="AD71" s="89"/>
-      <c r="AE71" s="90"/>
+      <c r="X71" s="93"/>
+      <c r="Y71" s="93"/>
+      <c r="Z71" s="93"/>
+      <c r="AA71" s="93"/>
+      <c r="AB71" s="93"/>
+      <c r="AC71" s="93"/>
+      <c r="AD71" s="93"/>
+      <c r="AE71" s="94"/>
       <c r="AF71" s="30" t="s">
         <v>682</v>
       </c>
@@ -13784,17 +14085,17 @@
       <c r="V72" s="9">
         <v>47473</v>
       </c>
-      <c r="W72" s="88" t="s">
+      <c r="W72" s="92" t="s">
         <v>690</v>
       </c>
-      <c r="X72" s="89"/>
-      <c r="Y72" s="89"/>
-      <c r="Z72" s="89"/>
-      <c r="AA72" s="89"/>
-      <c r="AB72" s="89"/>
-      <c r="AC72" s="89"/>
-      <c r="AD72" s="89"/>
-      <c r="AE72" s="90"/>
+      <c r="X72" s="93"/>
+      <c r="Y72" s="93"/>
+      <c r="Z72" s="93"/>
+      <c r="AA72" s="93"/>
+      <c r="AB72" s="93"/>
+      <c r="AC72" s="93"/>
+      <c r="AD72" s="93"/>
+      <c r="AE72" s="94"/>
       <c r="AF72" s="30" t="s">
         <v>691</v>
       </c>
@@ -13869,17 +14170,17 @@
       <c r="V73" s="9">
         <v>47519</v>
       </c>
-      <c r="W73" s="108" t="s">
+      <c r="W73" s="119" t="s">
         <v>699</v>
       </c>
-      <c r="X73" s="89"/>
-      <c r="Y73" s="89"/>
-      <c r="Z73" s="89"/>
-      <c r="AA73" s="89"/>
-      <c r="AB73" s="89"/>
-      <c r="AC73" s="89"/>
-      <c r="AD73" s="89"/>
-      <c r="AE73" s="90"/>
+      <c r="X73" s="93"/>
+      <c r="Y73" s="93"/>
+      <c r="Z73" s="93"/>
+      <c r="AA73" s="93"/>
+      <c r="AB73" s="93"/>
+      <c r="AC73" s="93"/>
+      <c r="AD73" s="93"/>
+      <c r="AE73" s="94"/>
       <c r="AF73" s="30" t="s">
         <v>700</v>
       </c>
@@ -13954,17 +14255,17 @@
       <c r="V74" s="43">
         <v>47521</v>
       </c>
-      <c r="W74" s="88" t="s">
+      <c r="W74" s="92" t="s">
         <v>707</v>
       </c>
-      <c r="X74" s="89"/>
-      <c r="Y74" s="89"/>
-      <c r="Z74" s="89"/>
-      <c r="AA74" s="89"/>
-      <c r="AB74" s="89"/>
-      <c r="AC74" s="89"/>
-      <c r="AD74" s="89"/>
-      <c r="AE74" s="90"/>
+      <c r="X74" s="93"/>
+      <c r="Y74" s="93"/>
+      <c r="Z74" s="93"/>
+      <c r="AA74" s="93"/>
+      <c r="AB74" s="93"/>
+      <c r="AC74" s="93"/>
+      <c r="AD74" s="93"/>
+      <c r="AE74" s="94"/>
       <c r="AF74" s="30" t="s">
         <v>708</v>
       </c>
@@ -14039,17 +14340,17 @@
       <c r="V75" s="9">
         <v>47527</v>
       </c>
-      <c r="W75" s="88" t="s">
+      <c r="W75" s="92" t="s">
         <v>716</v>
       </c>
-      <c r="X75" s="89"/>
-      <c r="Y75" s="89"/>
-      <c r="Z75" s="89"/>
-      <c r="AA75" s="89"/>
-      <c r="AB75" s="89"/>
-      <c r="AC75" s="89"/>
-      <c r="AD75" s="89"/>
-      <c r="AE75" s="90"/>
+      <c r="X75" s="93"/>
+      <c r="Y75" s="93"/>
+      <c r="Z75" s="93"/>
+      <c r="AA75" s="93"/>
+      <c r="AB75" s="93"/>
+      <c r="AC75" s="93"/>
+      <c r="AD75" s="93"/>
+      <c r="AE75" s="94"/>
       <c r="AF75" s="52" t="s">
         <v>717</v>
       </c>
@@ -14209,17 +14510,17 @@
       <c r="V77" s="9">
         <v>47528</v>
       </c>
-      <c r="W77" s="101" t="s">
+      <c r="W77" s="120" t="s">
         <v>733</v>
       </c>
-      <c r="X77" s="102"/>
-      <c r="Y77" s="102"/>
-      <c r="Z77" s="102"/>
-      <c r="AA77" s="102"/>
-      <c r="AB77" s="102"/>
-      <c r="AC77" s="102"/>
-      <c r="AD77" s="102"/>
-      <c r="AE77" s="103"/>
+      <c r="X77" s="121"/>
+      <c r="Y77" s="121"/>
+      <c r="Z77" s="121"/>
+      <c r="AA77" s="121"/>
+      <c r="AB77" s="121"/>
+      <c r="AC77" s="121"/>
+      <c r="AD77" s="121"/>
+      <c r="AE77" s="122"/>
       <c r="AF77" s="56" t="s">
         <v>734</v>
       </c>
@@ -14303,11 +14604,11 @@
       <c r="AC78" s="37"/>
       <c r="AD78" s="37"/>
       <c r="AE78" s="11"/>
-      <c r="AF78" s="98"/>
-      <c r="AG78" s="99"/>
-      <c r="AH78" s="99"/>
-      <c r="AI78" s="99"/>
-      <c r="AJ78" s="100"/>
+      <c r="AF78" s="99"/>
+      <c r="AG78" s="100"/>
+      <c r="AH78" s="100"/>
+      <c r="AI78" s="100"/>
+      <c r="AJ78" s="101"/>
       <c r="AK78" s="58"/>
     </row>
     <row r="79" spans="1:40" x14ac:dyDescent="0.3">
@@ -14386,11 +14687,11 @@
       <c r="AC79" s="37"/>
       <c r="AD79" s="37"/>
       <c r="AE79" s="11"/>
-      <c r="AF79" s="98"/>
-      <c r="AG79" s="99"/>
-      <c r="AH79" s="99"/>
-      <c r="AI79" s="99"/>
-      <c r="AJ79" s="100"/>
+      <c r="AF79" s="99"/>
+      <c r="AG79" s="100"/>
+      <c r="AH79" s="100"/>
+      <c r="AI79" s="100"/>
+      <c r="AJ79" s="101"/>
       <c r="AK79" s="58"/>
     </row>
     <row r="80" spans="1:40" x14ac:dyDescent="0.3">
@@ -14469,11 +14770,11 @@
       <c r="AC80" s="37"/>
       <c r="AD80" s="37"/>
       <c r="AE80" s="11"/>
-      <c r="AF80" s="98"/>
-      <c r="AG80" s="99"/>
-      <c r="AH80" s="99"/>
-      <c r="AI80" s="99"/>
-      <c r="AJ80" s="100"/>
+      <c r="AF80" s="99"/>
+      <c r="AG80" s="100"/>
+      <c r="AH80" s="100"/>
+      <c r="AI80" s="100"/>
+      <c r="AJ80" s="101"/>
       <c r="AK80" s="58"/>
     </row>
     <row r="81" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -14552,11 +14853,11 @@
       <c r="AC81" s="37"/>
       <c r="AD81" s="37"/>
       <c r="AE81" s="11"/>
-      <c r="AF81" s="98"/>
-      <c r="AG81" s="99"/>
-      <c r="AH81" s="99"/>
-      <c r="AI81" s="99"/>
-      <c r="AJ81" s="100"/>
+      <c r="AF81" s="99"/>
+      <c r="AG81" s="100"/>
+      <c r="AH81" s="100"/>
+      <c r="AI81" s="100"/>
+      <c r="AJ81" s="101"/>
       <c r="AK81" s="58"/>
     </row>
     <row r="82" spans="1:37" x14ac:dyDescent="0.3">
@@ -14995,6 +15296,105 @@
     </row>
   </sheetData>
   <mergeCells count="112">
+    <mergeCell ref="AF78:AJ78"/>
+    <mergeCell ref="AF79:AJ79"/>
+    <mergeCell ref="AF80:AJ80"/>
+    <mergeCell ref="AF81:AJ81"/>
+    <mergeCell ref="W71:AE71"/>
+    <mergeCell ref="W72:AE72"/>
+    <mergeCell ref="W73:AE73"/>
+    <mergeCell ref="W74:AE74"/>
+    <mergeCell ref="W75:AE75"/>
+    <mergeCell ref="W77:AE77"/>
+    <mergeCell ref="W67:AE67"/>
+    <mergeCell ref="AF67:AN67"/>
+    <mergeCell ref="W68:AE68"/>
+    <mergeCell ref="AF68:AN68"/>
+    <mergeCell ref="W69:AE69"/>
+    <mergeCell ref="W70:AE70"/>
+    <mergeCell ref="AF70:AI70"/>
+    <mergeCell ref="W62:AE62"/>
+    <mergeCell ref="AF62:AK62"/>
+    <mergeCell ref="W63:AE63"/>
+    <mergeCell ref="AF63:AK63"/>
+    <mergeCell ref="W64:AE64"/>
+    <mergeCell ref="W65:AE65"/>
+    <mergeCell ref="W57:AE57"/>
+    <mergeCell ref="AF57:AK57"/>
+    <mergeCell ref="W58:AE58"/>
+    <mergeCell ref="AF58:AK58"/>
+    <mergeCell ref="W61:AE61"/>
+    <mergeCell ref="AF61:AK61"/>
+    <mergeCell ref="W50:AE50"/>
+    <mergeCell ref="W52:AE52"/>
+    <mergeCell ref="W54:AE54"/>
+    <mergeCell ref="W55:AE55"/>
+    <mergeCell ref="AF55:AK55"/>
+    <mergeCell ref="W56:AE56"/>
+    <mergeCell ref="AF56:AK56"/>
+    <mergeCell ref="W47:AE47"/>
+    <mergeCell ref="AF47:AK47"/>
+    <mergeCell ref="W48:AE48"/>
+    <mergeCell ref="AF48:AK48"/>
+    <mergeCell ref="W49:AE49"/>
+    <mergeCell ref="AF49:AK49"/>
+    <mergeCell ref="W43:AE43"/>
+    <mergeCell ref="W44:AE44"/>
+    <mergeCell ref="AF44:AK44"/>
+    <mergeCell ref="W45:AE45"/>
+    <mergeCell ref="AF45:AK45"/>
+    <mergeCell ref="W46:AE46"/>
+    <mergeCell ref="AF46:AK46"/>
+    <mergeCell ref="W38:AE38"/>
+    <mergeCell ref="AF38:AK38"/>
+    <mergeCell ref="W39:AE39"/>
+    <mergeCell ref="AF39:AK39"/>
+    <mergeCell ref="W40:AE40"/>
+    <mergeCell ref="W42:AE42"/>
+    <mergeCell ref="AF42:AK42"/>
+    <mergeCell ref="W35:AE35"/>
+    <mergeCell ref="AF35:AK35"/>
+    <mergeCell ref="W36:AE36"/>
+    <mergeCell ref="AF36:AK36"/>
+    <mergeCell ref="W37:AE37"/>
+    <mergeCell ref="AF37:AK37"/>
+    <mergeCell ref="W31:AE31"/>
+    <mergeCell ref="AF31:AK31"/>
+    <mergeCell ref="W32:AE32"/>
+    <mergeCell ref="AF32:AK32"/>
+    <mergeCell ref="AF33:AK33"/>
+    <mergeCell ref="W34:AE34"/>
+    <mergeCell ref="AF34:AK34"/>
+    <mergeCell ref="W20:AE20"/>
+    <mergeCell ref="AF20:AK20"/>
+    <mergeCell ref="W21:AE21"/>
+    <mergeCell ref="AF21:AK21"/>
+    <mergeCell ref="W30:AE30"/>
+    <mergeCell ref="AF30:AK30"/>
+    <mergeCell ref="W17:AE17"/>
+    <mergeCell ref="AF17:AK17"/>
+    <mergeCell ref="W18:AE18"/>
+    <mergeCell ref="AF18:AK18"/>
+    <mergeCell ref="W19:AE19"/>
+    <mergeCell ref="AF19:AK19"/>
+    <mergeCell ref="W14:AE14"/>
+    <mergeCell ref="AF14:AK14"/>
+    <mergeCell ref="W15:AE15"/>
+    <mergeCell ref="AF15:AK15"/>
+    <mergeCell ref="W16:AE16"/>
+    <mergeCell ref="AF16:AK16"/>
+    <mergeCell ref="W11:AE11"/>
+    <mergeCell ref="AF11:AK11"/>
+    <mergeCell ref="W12:AE12"/>
+    <mergeCell ref="AF12:AK12"/>
+    <mergeCell ref="W13:AE13"/>
+    <mergeCell ref="AF13:AK13"/>
+    <mergeCell ref="W8:AE8"/>
+    <mergeCell ref="AF8:AK8"/>
+    <mergeCell ref="W9:AE9"/>
+    <mergeCell ref="AF9:AK9"/>
+    <mergeCell ref="W10:AE10"/>
+    <mergeCell ref="AF10:AK10"/>
     <mergeCell ref="W5:AE5"/>
     <mergeCell ref="AF5:AK5"/>
     <mergeCell ref="W6:AE6"/>
@@ -15008,105 +15408,6 @@
     <mergeCell ref="AF3:AK3"/>
     <mergeCell ref="W4:AE4"/>
     <mergeCell ref="AF4:AK4"/>
-    <mergeCell ref="W11:AE11"/>
-    <mergeCell ref="AF11:AK11"/>
-    <mergeCell ref="W12:AE12"/>
-    <mergeCell ref="AF12:AK12"/>
-    <mergeCell ref="W13:AE13"/>
-    <mergeCell ref="AF13:AK13"/>
-    <mergeCell ref="W8:AE8"/>
-    <mergeCell ref="AF8:AK8"/>
-    <mergeCell ref="W9:AE9"/>
-    <mergeCell ref="AF9:AK9"/>
-    <mergeCell ref="W10:AE10"/>
-    <mergeCell ref="AF10:AK10"/>
-    <mergeCell ref="W17:AE17"/>
-    <mergeCell ref="AF17:AK17"/>
-    <mergeCell ref="W18:AE18"/>
-    <mergeCell ref="AF18:AK18"/>
-    <mergeCell ref="W19:AE19"/>
-    <mergeCell ref="AF19:AK19"/>
-    <mergeCell ref="W14:AE14"/>
-    <mergeCell ref="AF14:AK14"/>
-    <mergeCell ref="W15:AE15"/>
-    <mergeCell ref="AF15:AK15"/>
-    <mergeCell ref="W16:AE16"/>
-    <mergeCell ref="AF16:AK16"/>
-    <mergeCell ref="W31:AE31"/>
-    <mergeCell ref="AF31:AK31"/>
-    <mergeCell ref="W32:AE32"/>
-    <mergeCell ref="AF32:AK32"/>
-    <mergeCell ref="AF33:AK33"/>
-    <mergeCell ref="W34:AE34"/>
-    <mergeCell ref="AF34:AK34"/>
-    <mergeCell ref="W20:AE20"/>
-    <mergeCell ref="AF20:AK20"/>
-    <mergeCell ref="W21:AE21"/>
-    <mergeCell ref="AF21:AK21"/>
-    <mergeCell ref="W30:AE30"/>
-    <mergeCell ref="AF30:AK30"/>
-    <mergeCell ref="W38:AE38"/>
-    <mergeCell ref="AF38:AK38"/>
-    <mergeCell ref="W39:AE39"/>
-    <mergeCell ref="AF39:AK39"/>
-    <mergeCell ref="W40:AE40"/>
-    <mergeCell ref="W42:AE42"/>
-    <mergeCell ref="AF42:AK42"/>
-    <mergeCell ref="W35:AE35"/>
-    <mergeCell ref="AF35:AK35"/>
-    <mergeCell ref="W36:AE36"/>
-    <mergeCell ref="AF36:AK36"/>
-    <mergeCell ref="W37:AE37"/>
-    <mergeCell ref="AF37:AK37"/>
-    <mergeCell ref="W47:AE47"/>
-    <mergeCell ref="AF47:AK47"/>
-    <mergeCell ref="W48:AE48"/>
-    <mergeCell ref="AF48:AK48"/>
-    <mergeCell ref="W49:AE49"/>
-    <mergeCell ref="AF49:AK49"/>
-    <mergeCell ref="W43:AE43"/>
-    <mergeCell ref="W44:AE44"/>
-    <mergeCell ref="AF44:AK44"/>
-    <mergeCell ref="W45:AE45"/>
-    <mergeCell ref="AF45:AK45"/>
-    <mergeCell ref="W46:AE46"/>
-    <mergeCell ref="AF46:AK46"/>
-    <mergeCell ref="W57:AE57"/>
-    <mergeCell ref="AF57:AK57"/>
-    <mergeCell ref="W58:AE58"/>
-    <mergeCell ref="AF58:AK58"/>
-    <mergeCell ref="W61:AE61"/>
-    <mergeCell ref="AF61:AK61"/>
-    <mergeCell ref="W50:AE50"/>
-    <mergeCell ref="W52:AE52"/>
-    <mergeCell ref="W54:AE54"/>
-    <mergeCell ref="W55:AE55"/>
-    <mergeCell ref="AF55:AK55"/>
-    <mergeCell ref="W56:AE56"/>
-    <mergeCell ref="AF56:AK56"/>
-    <mergeCell ref="W67:AE67"/>
-    <mergeCell ref="AF67:AN67"/>
-    <mergeCell ref="W68:AE68"/>
-    <mergeCell ref="AF68:AN68"/>
-    <mergeCell ref="W69:AE69"/>
-    <mergeCell ref="W70:AE70"/>
-    <mergeCell ref="AF70:AI70"/>
-    <mergeCell ref="W62:AE62"/>
-    <mergeCell ref="AF62:AK62"/>
-    <mergeCell ref="W63:AE63"/>
-    <mergeCell ref="AF63:AK63"/>
-    <mergeCell ref="W64:AE64"/>
-    <mergeCell ref="W65:AE65"/>
-    <mergeCell ref="AF78:AJ78"/>
-    <mergeCell ref="AF79:AJ79"/>
-    <mergeCell ref="AF80:AJ80"/>
-    <mergeCell ref="AF81:AJ81"/>
-    <mergeCell ref="W71:AE71"/>
-    <mergeCell ref="W72:AE72"/>
-    <mergeCell ref="W73:AE73"/>
-    <mergeCell ref="W74:AE74"/>
-    <mergeCell ref="W75:AE75"/>
-    <mergeCell ref="W77:AE77"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="AF6" r:id="rId1" xr:uid="{0570DCD9-7A91-4B9D-8F4C-EF55F90CCA32}"/>
@@ -15197,45 +15498,45 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:37" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="96" t="s">
         <v>809</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
-      <c r="H1" s="105"/>
-      <c r="I1" s="105"/>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="105"/>
-      <c r="O1" s="105"/>
-      <c r="P1" s="105"/>
-      <c r="Q1" s="105"/>
-      <c r="R1" s="105"/>
-      <c r="S1" s="105"/>
-      <c r="T1" s="105"/>
-      <c r="U1" s="105"/>
-      <c r="V1" s="105"/>
-      <c r="W1" s="105"/>
-      <c r="X1" s="105"/>
-      <c r="Y1" s="105"/>
-      <c r="Z1" s="105"/>
-      <c r="AA1" s="105"/>
-      <c r="AB1" s="105"/>
-      <c r="AC1" s="105"/>
-      <c r="AD1" s="105"/>
-      <c r="AE1" s="105"/>
-      <c r="AF1" s="105"/>
-      <c r="AG1" s="105"/>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="105"/>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="97"/>
+      <c r="I1" s="97"/>
+      <c r="J1" s="97"/>
+      <c r="K1" s="97"/>
+      <c r="L1" s="97"/>
+      <c r="M1" s="97"/>
+      <c r="N1" s="97"/>
+      <c r="O1" s="97"/>
+      <c r="P1" s="97"/>
+      <c r="Q1" s="97"/>
+      <c r="R1" s="97"/>
+      <c r="S1" s="97"/>
+      <c r="T1" s="97"/>
+      <c r="U1" s="97"/>
+      <c r="V1" s="97"/>
+      <c r="W1" s="97"/>
+      <c r="X1" s="97"/>
+      <c r="Y1" s="97"/>
+      <c r="Z1" s="97"/>
+      <c r="AA1" s="97"/>
+      <c r="AB1" s="97"/>
+      <c r="AC1" s="97"/>
+      <c r="AD1" s="97"/>
+      <c r="AE1" s="97"/>
+      <c r="AF1" s="97"/>
+      <c r="AG1" s="97"/>
+      <c r="AH1" s="97"/>
+      <c r="AI1" s="97"/>
+      <c r="AJ1" s="97"/>
+      <c r="AK1" s="97"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -15304,25 +15605,25 @@
       <c r="V2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="W2" s="106" t="s">
+      <c r="W2" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="106"/>
-      <c r="Y2" s="106"/>
-      <c r="Z2" s="106"/>
-      <c r="AA2" s="106"/>
-      <c r="AB2" s="106"/>
-      <c r="AC2" s="106"/>
-      <c r="AD2" s="106"/>
-      <c r="AE2" s="106"/>
-      <c r="AF2" s="107" t="s">
+      <c r="X2" s="98"/>
+      <c r="Y2" s="98"/>
+      <c r="Z2" s="98"/>
+      <c r="AA2" s="98"/>
+      <c r="AB2" s="98"/>
+      <c r="AC2" s="98"/>
+      <c r="AD2" s="98"/>
+      <c r="AE2" s="98"/>
+      <c r="AF2" s="91" t="s">
         <v>24</v>
       </c>
-      <c r="AG2" s="107"/>
-      <c r="AH2" s="107"/>
-      <c r="AI2" s="107"/>
-      <c r="AJ2" s="107"/>
-      <c r="AK2" s="107"/>
+      <c r="AG2" s="91"/>
+      <c r="AH2" s="91"/>
+      <c r="AI2" s="91"/>
+      <c r="AJ2" s="91"/>
+      <c r="AK2" s="91"/>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
@@ -15389,25 +15690,25 @@
       <c r="V3" s="9">
         <v>47908</v>
       </c>
-      <c r="W3" s="101" t="s">
+      <c r="W3" s="120" t="s">
         <v>819</v>
       </c>
-      <c r="X3" s="102"/>
-      <c r="Y3" s="102"/>
-      <c r="Z3" s="102"/>
-      <c r="AA3" s="102"/>
-      <c r="AB3" s="102"/>
-      <c r="AC3" s="102"/>
-      <c r="AD3" s="102"/>
-      <c r="AE3" s="103"/>
-      <c r="AF3" s="92" t="s">
+      <c r="X3" s="121"/>
+      <c r="Y3" s="121"/>
+      <c r="Z3" s="121"/>
+      <c r="AA3" s="121"/>
+      <c r="AB3" s="121"/>
+      <c r="AC3" s="121"/>
+      <c r="AD3" s="121"/>
+      <c r="AE3" s="122"/>
+      <c r="AF3" s="104" t="s">
         <v>820</v>
       </c>
-      <c r="AG3" s="89"/>
-      <c r="AH3" s="89"/>
-      <c r="AI3" s="89"/>
-      <c r="AJ3" s="89"/>
-      <c r="AK3" s="90"/>
+      <c r="AG3" s="93"/>
+      <c r="AH3" s="93"/>
+      <c r="AI3" s="93"/>
+      <c r="AJ3" s="93"/>
+      <c r="AK3" s="94"/>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
@@ -15474,25 +15775,25 @@
       <c r="V4" s="9">
         <v>229951</v>
       </c>
-      <c r="W4" s="88" t="s">
+      <c r="W4" s="92" t="s">
         <v>830</v>
       </c>
-      <c r="X4" s="89"/>
-      <c r="Y4" s="89"/>
-      <c r="Z4" s="89"/>
-      <c r="AA4" s="89"/>
-      <c r="AB4" s="89"/>
-      <c r="AC4" s="89"/>
-      <c r="AD4" s="89"/>
-      <c r="AE4" s="90"/>
-      <c r="AF4" s="92" t="s">
+      <c r="X4" s="93"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
+      <c r="AB4" s="93"/>
+      <c r="AC4" s="93"/>
+      <c r="AD4" s="93"/>
+      <c r="AE4" s="94"/>
+      <c r="AF4" s="104" t="s">
         <v>831</v>
       </c>
-      <c r="AG4" s="89"/>
-      <c r="AH4" s="89"/>
-      <c r="AI4" s="89"/>
-      <c r="AJ4" s="89"/>
-      <c r="AK4" s="90"/>
+      <c r="AG4" s="93"/>
+      <c r="AH4" s="93"/>
+      <c r="AI4" s="93"/>
+      <c r="AJ4" s="93"/>
+      <c r="AK4" s="94"/>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
@@ -15559,24 +15860,24 @@
       <c r="V5" s="9">
         <v>230067</v>
       </c>
-      <c r="W5" s="101" t="s">
+      <c r="W5" s="120" t="s">
         <v>841</v>
       </c>
-      <c r="X5" s="102"/>
-      <c r="Y5" s="102"/>
-      <c r="Z5" s="102"/>
-      <c r="AA5" s="102"/>
-      <c r="AB5" s="102"/>
-      <c r="AC5" s="102"/>
-      <c r="AD5" s="102"/>
-      <c r="AE5" s="103"/>
-      <c r="AF5" s="92" t="s">
+      <c r="X5" s="121"/>
+      <c r="Y5" s="121"/>
+      <c r="Z5" s="121"/>
+      <c r="AA5" s="121"/>
+      <c r="AB5" s="121"/>
+      <c r="AC5" s="121"/>
+      <c r="AD5" s="121"/>
+      <c r="AE5" s="122"/>
+      <c r="AF5" s="104" t="s">
         <v>842</v>
       </c>
-      <c r="AG5" s="89"/>
-      <c r="AH5" s="89"/>
-      <c r="AI5" s="89"/>
-      <c r="AJ5" s="90"/>
+      <c r="AG5" s="93"/>
+      <c r="AH5" s="93"/>
+      <c r="AI5" s="93"/>
+      <c r="AJ5" s="94"/>
       <c r="AK5" s="9"/>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.3">
@@ -15644,24 +15945,24 @@
       <c r="V6" s="9">
         <v>230066</v>
       </c>
-      <c r="W6" s="88" t="s">
+      <c r="W6" s="92" t="s">
         <v>841</v>
       </c>
-      <c r="X6" s="89"/>
-      <c r="Y6" s="89"/>
-      <c r="Z6" s="89"/>
-      <c r="AA6" s="89"/>
-      <c r="AB6" s="89"/>
-      <c r="AC6" s="89"/>
-      <c r="AD6" s="89"/>
-      <c r="AE6" s="90"/>
-      <c r="AF6" s="92" t="s">
+      <c r="X6" s="93"/>
+      <c r="Y6" s="93"/>
+      <c r="Z6" s="93"/>
+      <c r="AA6" s="93"/>
+      <c r="AB6" s="93"/>
+      <c r="AC6" s="93"/>
+      <c r="AD6" s="93"/>
+      <c r="AE6" s="94"/>
+      <c r="AF6" s="104" t="s">
         <v>851</v>
       </c>
-      <c r="AG6" s="89"/>
-      <c r="AH6" s="89"/>
-      <c r="AI6" s="89"/>
-      <c r="AJ6" s="90"/>
+      <c r="AG6" s="93"/>
+      <c r="AH6" s="93"/>
+      <c r="AI6" s="93"/>
+      <c r="AJ6" s="94"/>
       <c r="AK6" s="9"/>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.3">
@@ -15729,24 +16030,24 @@
       <c r="V7" s="9">
         <v>230065</v>
       </c>
-      <c r="W7" s="88" t="s">
+      <c r="W7" s="92" t="s">
         <v>841</v>
       </c>
-      <c r="X7" s="89"/>
-      <c r="Y7" s="89"/>
-      <c r="Z7" s="89"/>
-      <c r="AA7" s="89"/>
-      <c r="AB7" s="89"/>
-      <c r="AC7" s="89"/>
-      <c r="AD7" s="89"/>
-      <c r="AE7" s="90"/>
-      <c r="AF7" s="92" t="s">
+      <c r="X7" s="93"/>
+      <c r="Y7" s="93"/>
+      <c r="Z7" s="93"/>
+      <c r="AA7" s="93"/>
+      <c r="AB7" s="93"/>
+      <c r="AC7" s="93"/>
+      <c r="AD7" s="93"/>
+      <c r="AE7" s="94"/>
+      <c r="AF7" s="104" t="s">
         <v>859</v>
       </c>
-      <c r="AG7" s="89"/>
-      <c r="AH7" s="89"/>
-      <c r="AI7" s="89"/>
-      <c r="AJ7" s="90"/>
+      <c r="AG7" s="93"/>
+      <c r="AH7" s="93"/>
+      <c r="AI7" s="93"/>
+      <c r="AJ7" s="94"/>
       <c r="AK7" s="9"/>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.3">
@@ -15812,24 +16113,24 @@
       <c r="V8" s="9">
         <v>230047</v>
       </c>
-      <c r="W8" s="88" t="s">
+      <c r="W8" s="92" t="s">
         <v>866</v>
       </c>
-      <c r="X8" s="89"/>
-      <c r="Y8" s="89"/>
-      <c r="Z8" s="89"/>
-      <c r="AA8" s="89"/>
-      <c r="AB8" s="89"/>
-      <c r="AC8" s="89"/>
-      <c r="AD8" s="89"/>
-      <c r="AE8" s="90"/>
-      <c r="AF8" s="92" t="s">
+      <c r="X8" s="93"/>
+      <c r="Y8" s="93"/>
+      <c r="Z8" s="93"/>
+      <c r="AA8" s="93"/>
+      <c r="AB8" s="93"/>
+      <c r="AC8" s="93"/>
+      <c r="AD8" s="93"/>
+      <c r="AE8" s="94"/>
+      <c r="AF8" s="104" t="s">
         <v>867</v>
       </c>
-      <c r="AG8" s="89"/>
-      <c r="AH8" s="89"/>
-      <c r="AI8" s="89"/>
-      <c r="AJ8" s="90"/>
+      <c r="AG8" s="93"/>
+      <c r="AH8" s="93"/>
+      <c r="AI8" s="93"/>
+      <c r="AJ8" s="94"/>
       <c r="AK8" s="9"/>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.3">
@@ -15897,22 +16198,22 @@
       <c r="V9" s="9">
         <v>229993</v>
       </c>
-      <c r="W9" s="88" t="s">
+      <c r="W9" s="92" t="s">
         <v>874</v>
       </c>
-      <c r="X9" s="89"/>
-      <c r="Y9" s="89"/>
-      <c r="Z9" s="89"/>
-      <c r="AA9" s="89"/>
-      <c r="AB9" s="89"/>
-      <c r="AC9" s="89"/>
-      <c r="AD9" s="89"/>
-      <c r="AE9" s="90"/>
-      <c r="AF9" s="98"/>
-      <c r="AG9" s="99"/>
-      <c r="AH9" s="99"/>
-      <c r="AI9" s="99"/>
-      <c r="AJ9" s="100"/>
+      <c r="X9" s="93"/>
+      <c r="Y9" s="93"/>
+      <c r="Z9" s="93"/>
+      <c r="AA9" s="93"/>
+      <c r="AB9" s="93"/>
+      <c r="AC9" s="93"/>
+      <c r="AD9" s="93"/>
+      <c r="AE9" s="94"/>
+      <c r="AF9" s="99"/>
+      <c r="AG9" s="100"/>
+      <c r="AH9" s="100"/>
+      <c r="AI9" s="100"/>
+      <c r="AJ9" s="101"/>
       <c r="AK9" s="9"/>
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.3">
@@ -15980,24 +16281,24 @@
       <c r="V10" s="9">
         <v>47911</v>
       </c>
-      <c r="W10" s="88" t="s">
+      <c r="W10" s="92" t="s">
         <v>884</v>
       </c>
-      <c r="X10" s="89"/>
-      <c r="Y10" s="89"/>
-      <c r="Z10" s="89"/>
-      <c r="AA10" s="89"/>
-      <c r="AB10" s="89"/>
-      <c r="AC10" s="89"/>
-      <c r="AD10" s="89"/>
-      <c r="AE10" s="90"/>
-      <c r="AF10" s="92" t="s">
+      <c r="X10" s="93"/>
+      <c r="Y10" s="93"/>
+      <c r="Z10" s="93"/>
+      <c r="AA10" s="93"/>
+      <c r="AB10" s="93"/>
+      <c r="AC10" s="93"/>
+      <c r="AD10" s="93"/>
+      <c r="AE10" s="94"/>
+      <c r="AF10" s="104" t="s">
         <v>885</v>
       </c>
-      <c r="AG10" s="89"/>
-      <c r="AH10" s="89"/>
-      <c r="AI10" s="89"/>
-      <c r="AJ10" s="90"/>
+      <c r="AG10" s="93"/>
+      <c r="AH10" s="93"/>
+      <c r="AI10" s="93"/>
+      <c r="AJ10" s="94"/>
       <c r="AK10" s="9"/>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.3">
@@ -16065,24 +16366,24 @@
       <c r="V11" s="9">
         <v>47920</v>
       </c>
-      <c r="W11" s="88" t="s">
+      <c r="W11" s="92" t="s">
         <v>893</v>
       </c>
-      <c r="X11" s="89"/>
-      <c r="Y11" s="89"/>
-      <c r="Z11" s="89"/>
-      <c r="AA11" s="89"/>
-      <c r="AB11" s="89"/>
-      <c r="AC11" s="89"/>
-      <c r="AD11" s="89"/>
-      <c r="AE11" s="90"/>
-      <c r="AF11" s="92" t="s">
+      <c r="X11" s="93"/>
+      <c r="Y11" s="93"/>
+      <c r="Z11" s="93"/>
+      <c r="AA11" s="93"/>
+      <c r="AB11" s="93"/>
+      <c r="AC11" s="93"/>
+      <c r="AD11" s="93"/>
+      <c r="AE11" s="94"/>
+      <c r="AF11" s="104" t="s">
         <v>894</v>
       </c>
-      <c r="AG11" s="89"/>
-      <c r="AH11" s="89"/>
-      <c r="AI11" s="89"/>
-      <c r="AJ11" s="90"/>
+      <c r="AG11" s="93"/>
+      <c r="AH11" s="93"/>
+      <c r="AI11" s="93"/>
+      <c r="AJ11" s="94"/>
       <c r="AK11" s="9"/>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.3">
@@ -16150,24 +16451,24 @@
       <c r="V12" s="9">
         <v>47917</v>
       </c>
-      <c r="W12" s="88" t="s">
+      <c r="W12" s="92" t="s">
         <v>902</v>
       </c>
-      <c r="X12" s="89"/>
-      <c r="Y12" s="89"/>
-      <c r="Z12" s="89"/>
-      <c r="AA12" s="89"/>
-      <c r="AB12" s="89"/>
-      <c r="AC12" s="89"/>
-      <c r="AD12" s="89"/>
-      <c r="AE12" s="90"/>
-      <c r="AF12" s="92" t="s">
+      <c r="X12" s="93"/>
+      <c r="Y12" s="93"/>
+      <c r="Z12" s="93"/>
+      <c r="AA12" s="93"/>
+      <c r="AB12" s="93"/>
+      <c r="AC12" s="93"/>
+      <c r="AD12" s="93"/>
+      <c r="AE12" s="94"/>
+      <c r="AF12" s="104" t="s">
         <v>903</v>
       </c>
-      <c r="AG12" s="93"/>
-      <c r="AH12" s="93"/>
-      <c r="AI12" s="93"/>
-      <c r="AJ12" s="94"/>
+      <c r="AG12" s="107"/>
+      <c r="AH12" s="107"/>
+      <c r="AI12" s="107"/>
+      <c r="AJ12" s="108"/>
       <c r="AK12" s="9"/>
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.3">
@@ -16403,16 +16704,16 @@
       <c r="V15" s="9">
         <v>229905</v>
       </c>
-      <c r="W15" s="88" t="s">
+      <c r="W15" s="92" t="s">
         <v>931</v>
       </c>
-      <c r="X15" s="89"/>
-      <c r="Y15" s="89"/>
-      <c r="Z15" s="89"/>
-      <c r="AA15" s="89"/>
-      <c r="AB15" s="89"/>
-      <c r="AC15" s="89"/>
-      <c r="AD15" s="90"/>
+      <c r="X15" s="93"/>
+      <c r="Y15" s="93"/>
+      <c r="Z15" s="93"/>
+      <c r="AA15" s="93"/>
+      <c r="AB15" s="93"/>
+      <c r="AC15" s="93"/>
+      <c r="AD15" s="94"/>
       <c r="AE15" s="9"/>
       <c r="AF15" s="62" t="s">
         <v>932</v>
@@ -17591,16 +17892,16 @@
       <c r="V29" s="9">
         <v>229984</v>
       </c>
-      <c r="W29" s="95" t="s">
+      <c r="W29" s="109" t="s">
         <v>1069</v>
       </c>
-      <c r="X29" s="96"/>
-      <c r="Y29" s="96"/>
-      <c r="Z29" s="96"/>
-      <c r="AA29" s="96"/>
-      <c r="AB29" s="96"/>
-      <c r="AC29" s="96"/>
-      <c r="AD29" s="97"/>
+      <c r="X29" s="105"/>
+      <c r="Y29" s="105"/>
+      <c r="Z29" s="105"/>
+      <c r="AA29" s="105"/>
+      <c r="AB29" s="105"/>
+      <c r="AC29" s="105"/>
+      <c r="AD29" s="106"/>
       <c r="AE29" s="9"/>
       <c r="AF29" s="62" t="s">
         <v>1070</v>
@@ -17676,16 +17977,16 @@
       <c r="V30" s="9">
         <v>47953</v>
       </c>
-      <c r="W30" s="88" t="s">
+      <c r="W30" s="92" t="s">
         <v>1079</v>
       </c>
-      <c r="X30" s="89"/>
-      <c r="Y30" s="89"/>
-      <c r="Z30" s="89"/>
-      <c r="AA30" s="89"/>
-      <c r="AB30" s="89"/>
-      <c r="AC30" s="89"/>
-      <c r="AD30" s="90"/>
+      <c r="X30" s="93"/>
+      <c r="Y30" s="93"/>
+      <c r="Z30" s="93"/>
+      <c r="AA30" s="93"/>
+      <c r="AB30" s="93"/>
+      <c r="AC30" s="93"/>
+      <c r="AD30" s="94"/>
       <c r="AE30" s="9"/>
       <c r="AF30" s="62" t="s">
         <v>1080</v>
@@ -17761,16 +18062,16 @@
       <c r="V31" s="9">
         <v>47982</v>
       </c>
-      <c r="W31" s="91" t="s">
+      <c r="W31" s="103" t="s">
         <v>1090</v>
       </c>
-      <c r="X31" s="91"/>
-      <c r="Y31" s="91"/>
-      <c r="Z31" s="91"/>
-      <c r="AA31" s="91"/>
-      <c r="AB31" s="91"/>
-      <c r="AC31" s="91"/>
-      <c r="AD31" s="91"/>
+      <c r="X31" s="103"/>
+      <c r="Y31" s="103"/>
+      <c r="Z31" s="103"/>
+      <c r="AA31" s="103"/>
+      <c r="AB31" s="103"/>
+      <c r="AC31" s="103"/>
+      <c r="AD31" s="103"/>
       <c r="AE31" s="9"/>
       <c r="AF31" s="62" t="s">
         <v>1091</v>
@@ -17861,25 +18162,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="W4:AE4"/>
-    <mergeCell ref="AF4:AK4"/>
-    <mergeCell ref="A1:AK1"/>
-    <mergeCell ref="W2:AE2"/>
-    <mergeCell ref="AF2:AK2"/>
-    <mergeCell ref="W3:AE3"/>
-    <mergeCell ref="AF3:AK3"/>
-    <mergeCell ref="W5:AE5"/>
-    <mergeCell ref="AF5:AJ5"/>
-    <mergeCell ref="W6:AE6"/>
-    <mergeCell ref="AF6:AJ6"/>
-    <mergeCell ref="W7:AE7"/>
-    <mergeCell ref="AF7:AJ7"/>
-    <mergeCell ref="W8:AE8"/>
-    <mergeCell ref="AF8:AJ8"/>
-    <mergeCell ref="W9:AE9"/>
-    <mergeCell ref="AF9:AJ9"/>
-    <mergeCell ref="W10:AE10"/>
-    <mergeCell ref="AF10:AJ10"/>
     <mergeCell ref="W30:AD30"/>
     <mergeCell ref="W31:AD31"/>
     <mergeCell ref="W11:AE11"/>
@@ -17888,6 +18170,25 @@
     <mergeCell ref="AF12:AJ12"/>
     <mergeCell ref="W15:AD15"/>
     <mergeCell ref="W29:AD29"/>
+    <mergeCell ref="W8:AE8"/>
+    <mergeCell ref="AF8:AJ8"/>
+    <mergeCell ref="W9:AE9"/>
+    <mergeCell ref="AF9:AJ9"/>
+    <mergeCell ref="W10:AE10"/>
+    <mergeCell ref="AF10:AJ10"/>
+    <mergeCell ref="W5:AE5"/>
+    <mergeCell ref="AF5:AJ5"/>
+    <mergeCell ref="W6:AE6"/>
+    <mergeCell ref="AF6:AJ6"/>
+    <mergeCell ref="W7:AE7"/>
+    <mergeCell ref="AF7:AJ7"/>
+    <mergeCell ref="W4:AE4"/>
+    <mergeCell ref="AF4:AK4"/>
+    <mergeCell ref="A1:AK1"/>
+    <mergeCell ref="W2:AE2"/>
+    <mergeCell ref="AF2:AK2"/>
+    <mergeCell ref="W3:AE3"/>
+    <mergeCell ref="AF3:AK3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="AF3" r:id="rId1" xr:uid="{3E9D2EC9-B76E-4512-B3E3-1DF2669B44B6}"/>
@@ -18639,49 +18940,49 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE55D0B5-A946-43E7-B8C4-DABFA6F5BDF5}">
-  <dimension ref="A1:AK76"/>
+  <dimension ref="A1:AK84"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:37" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="90" t="s">
         <v>1166</v>
       </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="120"/>
-      <c r="U1" s="120"/>
-      <c r="V1" s="120"/>
-      <c r="W1" s="120"/>
-      <c r="X1" s="120"/>
-      <c r="Y1" s="120"/>
-      <c r="Z1" s="120"/>
-      <c r="AA1" s="120"/>
-      <c r="AB1" s="120"/>
-      <c r="AC1" s="120"/>
-      <c r="AD1" s="120"/>
-      <c r="AE1" s="120"/>
-      <c r="AF1" s="120"/>
-      <c r="AG1" s="120"/>
-      <c r="AH1" s="120"/>
-      <c r="AI1" s="120"/>
-      <c r="AJ1" s="120"/>
-      <c r="AK1" s="120"/>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="90"/>
+      <c r="H1" s="90"/>
+      <c r="I1" s="90"/>
+      <c r="J1" s="90"/>
+      <c r="K1" s="90"/>
+      <c r="L1" s="90"/>
+      <c r="M1" s="90"/>
+      <c r="N1" s="90"/>
+      <c r="O1" s="90"/>
+      <c r="P1" s="90"/>
+      <c r="Q1" s="90"/>
+      <c r="R1" s="90"/>
+      <c r="S1" s="90"/>
+      <c r="T1" s="90"/>
+      <c r="U1" s="90"/>
+      <c r="V1" s="90"/>
+      <c r="W1" s="90"/>
+      <c r="X1" s="90"/>
+      <c r="Y1" s="90"/>
+      <c r="Z1" s="90"/>
+      <c r="AA1" s="90"/>
+      <c r="AB1" s="90"/>
+      <c r="AC1" s="90"/>
+      <c r="AD1" s="90"/>
+      <c r="AE1" s="90"/>
+      <c r="AF1" s="90"/>
+      <c r="AG1" s="90"/>
+      <c r="AH1" s="90"/>
+      <c r="AI1" s="90"/>
+      <c r="AJ1" s="90"/>
+      <c r="AK1" s="90"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -24502,32 +24803,68 @@
       <c r="AK75" s="9"/>
     </row>
     <row r="76" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A76" s="9">
-        <v>74</v>
-      </c>
-      <c r="B76" s="9"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="9"/>
-      <c r="F76" s="9"/>
-      <c r="G76" s="9"/>
-      <c r="H76" s="9"/>
-      <c r="I76" s="9"/>
-      <c r="J76" s="9"/>
-      <c r="K76" s="9"/>
-      <c r="L76" s="9"/>
-      <c r="M76" s="9"/>
-      <c r="N76" s="9"/>
-      <c r="O76" s="9"/>
-      <c r="P76" s="9"/>
-      <c r="Q76" s="9"/>
-      <c r="R76" s="9"/>
-      <c r="S76" s="9"/>
-      <c r="T76" s="9"/>
-      <c r="U76" s="9"/>
-      <c r="V76" s="9"/>
-      <c r="W76" s="9"/>
-      <c r="X76" s="9"/>
+      <c r="A76" s="124">
+        <v>76</v>
+      </c>
+      <c r="B76" s="124" t="s">
+        <v>25</v>
+      </c>
+      <c r="C76" s="124" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D76" s="124" t="s">
+        <v>2242</v>
+      </c>
+      <c r="E76" s="124" t="s">
+        <v>2243</v>
+      </c>
+      <c r="F76" s="124" t="s">
+        <v>813</v>
+      </c>
+      <c r="G76" s="125">
+        <v>39816</v>
+      </c>
+      <c r="H76" s="124" t="s">
+        <v>2244</v>
+      </c>
+      <c r="I76" s="124" t="s">
+        <v>2245</v>
+      </c>
+      <c r="J76" s="124">
+        <v>8890216590</v>
+      </c>
+      <c r="K76" s="124">
+        <v>9448566407</v>
+      </c>
+      <c r="L76" s="126" t="s">
+        <v>2246</v>
+      </c>
+      <c r="M76" s="126" t="s">
+        <v>2247</v>
+      </c>
+      <c r="N76" s="124"/>
+      <c r="O76" s="124" t="s">
+        <v>2248</v>
+      </c>
+      <c r="P76" s="124" t="s">
+        <v>2249</v>
+      </c>
+      <c r="Q76" s="124">
+        <v>600</v>
+      </c>
+      <c r="R76" s="124">
+        <v>59.5</v>
+      </c>
+      <c r="S76" s="124">
+        <v>357</v>
+      </c>
+      <c r="T76" s="124"/>
+      <c r="U76" s="124"/>
+      <c r="V76" s="124"/>
+      <c r="W76" s="124" t="s">
+        <v>2250</v>
+      </c>
+      <c r="X76" s="124"/>
       <c r="Y76" s="9"/>
       <c r="Z76" s="9"/>
       <c r="AA76" s="9"/>
@@ -24541,6 +24878,610 @@
       <c r="AI76" s="9"/>
       <c r="AJ76" s="9"/>
       <c r="AK76" s="9"/>
+    </row>
+    <row r="77" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A77" s="128">
+        <v>77</v>
+      </c>
+      <c r="B77" s="128" t="s">
+        <v>25</v>
+      </c>
+      <c r="C77" s="128" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D77" s="128" t="s">
+        <v>2251</v>
+      </c>
+      <c r="E77" s="128" t="s">
+        <v>2252</v>
+      </c>
+      <c r="F77" s="128" t="s">
+        <v>813</v>
+      </c>
+      <c r="G77" s="129">
+        <v>39605</v>
+      </c>
+      <c r="H77" s="128" t="s">
+        <v>2253</v>
+      </c>
+      <c r="I77" s="128" t="s">
+        <v>2254</v>
+      </c>
+      <c r="J77" s="128">
+        <v>7892300925</v>
+      </c>
+      <c r="K77" s="128">
+        <v>8123974407</v>
+      </c>
+      <c r="L77" s="130" t="s">
+        <v>2255</v>
+      </c>
+      <c r="M77" s="130" t="s">
+        <v>2256</v>
+      </c>
+      <c r="N77" s="128"/>
+      <c r="O77" s="128" t="s">
+        <v>2248</v>
+      </c>
+      <c r="P77" s="128" t="s">
+        <v>2249</v>
+      </c>
+      <c r="Q77" s="128">
+        <v>600</v>
+      </c>
+      <c r="R77" s="128"/>
+      <c r="S77" s="128">
+        <v>291</v>
+      </c>
+      <c r="T77" s="128"/>
+      <c r="U77" s="128"/>
+      <c r="V77" s="128"/>
+      <c r="W77" s="128" t="s">
+        <v>2257</v>
+      </c>
+      <c r="X77" s="128"/>
+      <c r="Y77" s="123"/>
+      <c r="Z77" s="123"/>
+      <c r="AA77" s="123"/>
+      <c r="AB77" s="123"/>
+      <c r="AC77" s="123"/>
+      <c r="AD77" s="123"/>
+      <c r="AE77" s="123"/>
+      <c r="AF77" s="123"/>
+      <c r="AG77" s="123"/>
+      <c r="AH77" s="123"/>
+      <c r="AI77" s="123"/>
+      <c r="AJ77" s="123"/>
+      <c r="AK77" s="123"/>
+    </row>
+    <row r="78" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A78" s="132">
+        <v>74</v>
+      </c>
+      <c r="B78" s="132" t="s">
+        <v>25</v>
+      </c>
+      <c r="C78" s="132" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D78" s="132" t="s">
+        <v>2258</v>
+      </c>
+      <c r="E78" s="132" t="s">
+        <v>2259</v>
+      </c>
+      <c r="F78" s="132" t="s">
+        <v>813</v>
+      </c>
+      <c r="G78" s="133">
+        <v>39646</v>
+      </c>
+      <c r="H78" s="132" t="s">
+        <v>2260</v>
+      </c>
+      <c r="I78" s="132" t="s">
+        <v>2261</v>
+      </c>
+      <c r="J78" s="132">
+        <v>9742138873</v>
+      </c>
+      <c r="K78" s="132">
+        <v>9845556843</v>
+      </c>
+      <c r="L78" s="134" t="s">
+        <v>1843</v>
+      </c>
+      <c r="M78" s="134" t="s">
+        <v>1798</v>
+      </c>
+      <c r="N78" s="132"/>
+      <c r="O78" s="132" t="s">
+        <v>91</v>
+      </c>
+      <c r="P78" s="132" t="s">
+        <v>2262</v>
+      </c>
+      <c r="Q78" s="132">
+        <v>600</v>
+      </c>
+      <c r="R78" s="132">
+        <v>88.5</v>
+      </c>
+      <c r="S78" s="132">
+        <v>475</v>
+      </c>
+      <c r="T78" s="132"/>
+      <c r="U78" s="132"/>
+      <c r="V78" s="132"/>
+      <c r="W78" s="132" t="s">
+        <v>2263</v>
+      </c>
+      <c r="X78" s="135" t="s">
+        <v>1845</v>
+      </c>
+      <c r="Y78" s="127"/>
+      <c r="Z78" s="127"/>
+      <c r="AA78" s="127"/>
+      <c r="AB78" s="127"/>
+      <c r="AC78" s="127"/>
+      <c r="AD78" s="127"/>
+      <c r="AE78" s="127"/>
+      <c r="AF78" s="127"/>
+      <c r="AG78" s="127"/>
+      <c r="AH78" s="127"/>
+      <c r="AI78" s="127"/>
+      <c r="AJ78" s="127"/>
+      <c r="AK78" s="127"/>
+    </row>
+    <row r="79" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A79" s="137">
+        <v>78</v>
+      </c>
+      <c r="B79" s="137" t="s">
+        <v>25</v>
+      </c>
+      <c r="C79" s="137" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D79" s="137" t="s">
+        <v>2264</v>
+      </c>
+      <c r="E79" s="137" t="s">
+        <v>2265</v>
+      </c>
+      <c r="F79" s="137" t="s">
+        <v>813</v>
+      </c>
+      <c r="G79" s="138">
+        <v>39815</v>
+      </c>
+      <c r="H79" s="137" t="s">
+        <v>2266</v>
+      </c>
+      <c r="I79" s="137" t="s">
+        <v>2267</v>
+      </c>
+      <c r="J79" s="137">
+        <v>9686874060</v>
+      </c>
+      <c r="K79" s="137">
+        <v>9740359009</v>
+      </c>
+      <c r="L79" s="139" t="s">
+        <v>2268</v>
+      </c>
+      <c r="M79" s="139" t="s">
+        <v>2269</v>
+      </c>
+      <c r="N79" s="137"/>
+      <c r="O79" s="137" t="s">
+        <v>91</v>
+      </c>
+      <c r="P79" s="137" t="s">
+        <v>1239</v>
+      </c>
+      <c r="Q79" s="137">
+        <v>600</v>
+      </c>
+      <c r="R79" s="137">
+        <v>65.5</v>
+      </c>
+      <c r="S79" s="137">
+        <v>393</v>
+      </c>
+      <c r="T79" s="137"/>
+      <c r="U79" s="137"/>
+      <c r="V79" s="137"/>
+      <c r="W79" s="137" t="s">
+        <v>2270</v>
+      </c>
+      <c r="X79" s="140" t="s">
+        <v>2271</v>
+      </c>
+      <c r="Y79" s="131"/>
+      <c r="Z79" s="131"/>
+      <c r="AA79" s="131"/>
+      <c r="AB79" s="131"/>
+      <c r="AC79" s="131"/>
+      <c r="AD79" s="131"/>
+      <c r="AE79" s="131"/>
+      <c r="AF79" s="131"/>
+      <c r="AG79" s="131"/>
+      <c r="AH79" s="131"/>
+      <c r="AI79" s="131"/>
+      <c r="AJ79" s="131"/>
+      <c r="AK79" s="131"/>
+    </row>
+    <row r="80" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A80" s="142">
+        <v>86</v>
+      </c>
+      <c r="B80" s="142" t="s">
+        <v>25</v>
+      </c>
+      <c r="C80" s="142" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D80" s="142" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E80" s="142" t="s">
+        <v>2273</v>
+      </c>
+      <c r="F80" s="142" t="s">
+        <v>813</v>
+      </c>
+      <c r="G80" s="143">
+        <v>39668</v>
+      </c>
+      <c r="H80" s="143" t="s">
+        <v>2274</v>
+      </c>
+      <c r="I80" s="142" t="s">
+        <v>2275</v>
+      </c>
+      <c r="J80" s="142">
+        <v>9019002260</v>
+      </c>
+      <c r="K80" s="142">
+        <v>6361142792</v>
+      </c>
+      <c r="L80" s="144" t="s">
+        <v>2276</v>
+      </c>
+      <c r="M80" s="144" t="s">
+        <v>2277</v>
+      </c>
+      <c r="N80" s="144"/>
+      <c r="O80" s="142" t="s">
+        <v>91</v>
+      </c>
+      <c r="P80" s="142" t="s">
+        <v>1239</v>
+      </c>
+      <c r="Q80" s="142">
+        <v>600</v>
+      </c>
+      <c r="R80" s="142">
+        <v>65</v>
+      </c>
+      <c r="S80" s="142">
+        <v>388</v>
+      </c>
+      <c r="T80" s="143">
+        <v>46191</v>
+      </c>
+      <c r="U80" s="142"/>
+      <c r="V80" s="142"/>
+      <c r="W80" s="142" t="s">
+        <v>2278</v>
+      </c>
+      <c r="X80" s="145" t="s">
+        <v>2279</v>
+      </c>
+      <c r="Y80" s="141"/>
+      <c r="Z80" s="136"/>
+      <c r="AA80" s="136"/>
+      <c r="AB80" s="136"/>
+      <c r="AC80" s="136"/>
+      <c r="AD80" s="136"/>
+      <c r="AE80" s="136"/>
+      <c r="AF80" s="136"/>
+      <c r="AG80" s="136"/>
+      <c r="AH80" s="136"/>
+      <c r="AI80" s="136"/>
+      <c r="AJ80" s="136"/>
+      <c r="AK80" s="136"/>
+    </row>
+    <row r="81" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A81" s="147">
+        <v>79</v>
+      </c>
+      <c r="B81" s="147" t="s">
+        <v>25</v>
+      </c>
+      <c r="C81" s="147" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D81" s="147" t="s">
+        <v>2280</v>
+      </c>
+      <c r="E81" s="147" t="s">
+        <v>2281</v>
+      </c>
+      <c r="F81" s="147" t="s">
+        <v>845</v>
+      </c>
+      <c r="G81" s="148">
+        <v>39503</v>
+      </c>
+      <c r="H81" s="147" t="s">
+        <v>2282</v>
+      </c>
+      <c r="I81" s="147" t="s">
+        <v>2283</v>
+      </c>
+      <c r="J81" s="147">
+        <v>8088038940</v>
+      </c>
+      <c r="K81" s="147">
+        <v>7996999030</v>
+      </c>
+      <c r="L81" s="149" t="s">
+        <v>2284</v>
+      </c>
+      <c r="M81" s="149" t="s">
+        <v>2285</v>
+      </c>
+      <c r="N81" s="147"/>
+      <c r="O81" s="147" t="s">
+        <v>36</v>
+      </c>
+      <c r="P81" s="147" t="s">
+        <v>2286</v>
+      </c>
+      <c r="Q81" s="147">
+        <v>600</v>
+      </c>
+      <c r="R81" s="147">
+        <v>58.5</v>
+      </c>
+      <c r="S81" s="147">
+        <v>351</v>
+      </c>
+      <c r="T81" s="147"/>
+      <c r="U81" s="147"/>
+      <c r="V81" s="147"/>
+      <c r="W81" s="147" t="s">
+        <v>2287</v>
+      </c>
+      <c r="X81" s="150" t="s">
+        <v>2288</v>
+      </c>
+      <c r="Y81" s="146"/>
+      <c r="Z81" s="141"/>
+      <c r="AA81" s="141"/>
+      <c r="AB81" s="141"/>
+      <c r="AC81" s="141"/>
+      <c r="AD81" s="141"/>
+      <c r="AE81" s="141"/>
+      <c r="AF81" s="141"/>
+      <c r="AG81" s="141"/>
+      <c r="AH81" s="141"/>
+      <c r="AI81" s="141"/>
+      <c r="AJ81" s="141"/>
+      <c r="AK81" s="141"/>
+    </row>
+    <row r="82" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A82" s="152">
+        <v>80</v>
+      </c>
+      <c r="B82" s="152" t="s">
+        <v>25</v>
+      </c>
+      <c r="C82" s="152" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D82" s="152" t="s">
+        <v>2289</v>
+      </c>
+      <c r="E82" s="152" t="s">
+        <v>2290</v>
+      </c>
+      <c r="F82" s="152" t="s">
+        <v>845</v>
+      </c>
+      <c r="G82" s="153">
+        <v>39270</v>
+      </c>
+      <c r="H82" s="152" t="s">
+        <v>2291</v>
+      </c>
+      <c r="I82" s="152" t="s">
+        <v>1724</v>
+      </c>
+      <c r="J82" s="152">
+        <v>9739031585</v>
+      </c>
+      <c r="K82" s="152">
+        <v>7975893845</v>
+      </c>
+      <c r="L82" s="154" t="s">
+        <v>2292</v>
+      </c>
+      <c r="M82" s="154" t="s">
+        <v>2293</v>
+      </c>
+      <c r="N82" s="152"/>
+      <c r="O82" s="152" t="s">
+        <v>91</v>
+      </c>
+      <c r="P82" s="152" t="s">
+        <v>1239</v>
+      </c>
+      <c r="Q82" s="152">
+        <v>600</v>
+      </c>
+      <c r="R82" s="152">
+        <v>63.5</v>
+      </c>
+      <c r="S82" s="152">
+        <v>381</v>
+      </c>
+      <c r="T82" s="152"/>
+      <c r="U82" s="152"/>
+      <c r="V82" s="152"/>
+      <c r="W82" s="152" t="s">
+        <v>2294</v>
+      </c>
+      <c r="X82" s="155" t="s">
+        <v>2295</v>
+      </c>
+    </row>
+    <row r="83" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A83" s="157">
+        <v>85</v>
+      </c>
+      <c r="B83" s="157" t="s">
+        <v>25</v>
+      </c>
+      <c r="C83" s="157" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D83" s="157" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E83" s="157" t="s">
+        <v>2296</v>
+      </c>
+      <c r="F83" s="157" t="s">
+        <v>845</v>
+      </c>
+      <c r="G83" s="158">
+        <v>39383</v>
+      </c>
+      <c r="H83" s="158" t="s">
+        <v>2297</v>
+      </c>
+      <c r="I83" s="157" t="s">
+        <v>2298</v>
+      </c>
+      <c r="J83" s="157">
+        <v>9743285751</v>
+      </c>
+      <c r="K83" s="157">
+        <v>9743009325</v>
+      </c>
+      <c r="L83" s="159" t="s">
+        <v>2299</v>
+      </c>
+      <c r="M83" s="159" t="s">
+        <v>2300</v>
+      </c>
+      <c r="N83" s="159"/>
+      <c r="O83" s="157" t="s">
+        <v>36</v>
+      </c>
+      <c r="P83" s="157" t="s">
+        <v>1215</v>
+      </c>
+      <c r="Q83" s="157">
+        <v>600</v>
+      </c>
+      <c r="R83" s="157">
+        <v>87.5</v>
+      </c>
+      <c r="S83" s="157">
+        <v>525</v>
+      </c>
+      <c r="T83" s="158">
+        <v>46248</v>
+      </c>
+      <c r="U83" s="157"/>
+      <c r="V83" s="157"/>
+      <c r="W83" s="157" t="s">
+        <v>2301</v>
+      </c>
+      <c r="X83" s="160" t="s">
+        <v>2302</v>
+      </c>
+      <c r="Y83" s="156"/>
+      <c r="Z83" s="151"/>
+      <c r="AA83" s="151"/>
+      <c r="AB83" s="151"/>
+      <c r="AC83" s="151"/>
+      <c r="AD83" s="151"/>
+      <c r="AE83" s="151"/>
+      <c r="AF83" s="151"/>
+      <c r="AG83" s="151"/>
+      <c r="AH83" s="151"/>
+      <c r="AI83" s="151"/>
+      <c r="AJ83" s="151"/>
+      <c r="AK83" s="151"/>
+    </row>
+    <row r="84" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A84" s="162">
+        <v>75</v>
+      </c>
+      <c r="B84" s="162" t="s">
+        <v>25</v>
+      </c>
+      <c r="C84" s="162" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D84" s="162" t="s">
+        <v>2303</v>
+      </c>
+      <c r="E84" s="162" t="s">
+        <v>2304</v>
+      </c>
+      <c r="F84" s="162" t="s">
+        <v>813</v>
+      </c>
+      <c r="G84" s="163">
+        <v>39647</v>
+      </c>
+      <c r="H84" s="162" t="s">
+        <v>2305</v>
+      </c>
+      <c r="I84" s="162" t="s">
+        <v>2306</v>
+      </c>
+      <c r="J84" s="162">
+        <v>9886539418</v>
+      </c>
+      <c r="K84" s="162">
+        <v>9886292272</v>
+      </c>
+      <c r="L84" s="164" t="s">
+        <v>2307</v>
+      </c>
+      <c r="M84" s="162"/>
+      <c r="N84" s="162"/>
+      <c r="O84" s="162" t="s">
+        <v>80</v>
+      </c>
+      <c r="P84" s="162" t="s">
+        <v>1300</v>
+      </c>
+      <c r="Q84" s="162">
+        <v>600</v>
+      </c>
+      <c r="R84" s="162">
+        <v>42</v>
+      </c>
+      <c r="S84" s="162">
+        <v>250</v>
+      </c>
+      <c r="T84" s="162"/>
+      <c r="U84" s="162"/>
+      <c r="V84" s="162"/>
+      <c r="W84" s="162" t="s">
+        <v>2308</v>
+      </c>
+      <c r="X84" s="165" t="s">
+        <v>2309</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -24600,6 +25541,13 @@
     <hyperlink ref="X70" r:id="rId51" xr:uid="{0943BFF5-8F68-4DB1-B021-145C163A0629}"/>
     <hyperlink ref="X75" r:id="rId52" xr:uid="{0A23151E-2DCE-4605-8ECA-67E3241E524E}"/>
     <hyperlink ref="X73" r:id="rId53" xr:uid="{13A0AAEC-B583-4C68-828E-F728E11BA009}"/>
+    <hyperlink ref="X78" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="X79" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="X80" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="X81" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="X82" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="X83" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="X84" r:id="rId60" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -24635,43 +25583,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="90" t="s">
         <v>1685</v>
       </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="120"/>
-      <c r="U1" s="120"/>
-      <c r="V1" s="120"/>
-      <c r="W1" s="120"/>
-      <c r="X1" s="120"/>
-      <c r="Y1" s="120"/>
-      <c r="Z1" s="120"/>
-      <c r="AA1" s="120"/>
-      <c r="AB1" s="120"/>
-      <c r="AC1" s="120"/>
-      <c r="AD1" s="120"/>
-      <c r="AE1" s="120"/>
-      <c r="AF1" s="120"/>
-      <c r="AG1" s="120"/>
-      <c r="AH1" s="120"/>
-      <c r="AI1" s="120"/>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="90"/>
+      <c r="H1" s="90"/>
+      <c r="I1" s="90"/>
+      <c r="J1" s="90"/>
+      <c r="K1" s="90"/>
+      <c r="L1" s="90"/>
+      <c r="M1" s="90"/>
+      <c r="N1" s="90"/>
+      <c r="O1" s="90"/>
+      <c r="P1" s="90"/>
+      <c r="Q1" s="90"/>
+      <c r="R1" s="90"/>
+      <c r="S1" s="90"/>
+      <c r="T1" s="90"/>
+      <c r="U1" s="90"/>
+      <c r="V1" s="90"/>
+      <c r="W1" s="90"/>
+      <c r="X1" s="90"/>
+      <c r="Y1" s="90"/>
+      <c r="Z1" s="90"/>
+      <c r="AA1" s="90"/>
+      <c r="AB1" s="90"/>
+      <c r="AC1" s="90"/>
+      <c r="AD1" s="90"/>
+      <c r="AE1" s="90"/>
+      <c r="AF1" s="90"/>
+      <c r="AG1" s="90"/>
+      <c r="AH1" s="90"/>
+      <c r="AI1" s="90"/>
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -24751,12 +25699,12 @@
       <c r="AA2" s="2"/>
       <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
-      <c r="AD2" s="107"/>
-      <c r="AE2" s="107"/>
-      <c r="AF2" s="107"/>
-      <c r="AG2" s="107"/>
-      <c r="AH2" s="107"/>
-      <c r="AI2" s="107"/>
+      <c r="AD2" s="91"/>
+      <c r="AE2" s="91"/>
+      <c r="AF2" s="91"/>
+      <c r="AG2" s="91"/>
+      <c r="AH2" s="91"/>
+      <c r="AI2" s="91"/>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="9">
@@ -24909,12 +25857,12 @@
       <c r="AA4" s="9"/>
       <c r="AB4" s="9"/>
       <c r="AC4" s="9"/>
-      <c r="AD4" s="107"/>
-      <c r="AE4" s="107"/>
-      <c r="AF4" s="107"/>
-      <c r="AG4" s="107"/>
-      <c r="AH4" s="107"/>
-      <c r="AI4" s="107"/>
+      <c r="AD4" s="91"/>
+      <c r="AE4" s="91"/>
+      <c r="AF4" s="91"/>
+      <c r="AG4" s="91"/>
+      <c r="AH4" s="91"/>
+      <c r="AI4" s="91"/>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
@@ -27281,17 +28229,17 @@
       <c r="X1" s="2" t="s">
         <v>1168</v>
       </c>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
-      <c r="AC1" s="121"/>
-      <c r="AD1" s="121"/>
-      <c r="AE1" s="121"/>
-      <c r="AF1" s="121"/>
-      <c r="AG1" s="121"/>
-      <c r="AH1" s="121"/>
-      <c r="AI1" s="121"/>
+      <c r="Y1" s="88"/>
+      <c r="Z1" s="88"/>
+      <c r="AA1" s="88"/>
+      <c r="AB1" s="88"/>
+      <c r="AC1" s="88"/>
+      <c r="AD1" s="88"/>
+      <c r="AE1" s="88"/>
+      <c r="AF1" s="88"/>
+      <c r="AG1" s="88"/>
+      <c r="AH1" s="88"/>
+      <c r="AI1" s="88"/>
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="9">
@@ -27359,12 +28307,12 @@
       <c r="AA2" s="2"/>
       <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
-      <c r="AD2" s="107"/>
-      <c r="AE2" s="107"/>
-      <c r="AF2" s="107"/>
-      <c r="AG2" s="107"/>
-      <c r="AH2" s="107"/>
-      <c r="AI2" s="107"/>
+      <c r="AD2" s="91"/>
+      <c r="AE2" s="91"/>
+      <c r="AF2" s="91"/>
+      <c r="AG2" s="91"/>
+      <c r="AH2" s="91"/>
+      <c r="AI2" s="91"/>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="9">
@@ -27511,12 +28459,12 @@
       <c r="AA4" s="9"/>
       <c r="AB4" s="9"/>
       <c r="AC4" s="9"/>
-      <c r="AD4" s="107"/>
-      <c r="AE4" s="107"/>
-      <c r="AF4" s="107"/>
-      <c r="AG4" s="107"/>
-      <c r="AH4" s="107"/>
-      <c r="AI4" s="107"/>
+      <c r="AD4" s="91"/>
+      <c r="AE4" s="91"/>
+      <c r="AF4" s="91"/>
+      <c r="AG4" s="91"/>
+      <c r="AH4" s="91"/>
+      <c r="AI4" s="91"/>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
@@ -27654,7 +28602,7 @@
       </c>
       <c r="U6" s="9"/>
       <c r="V6" s="9"/>
-      <c r="W6" s="122" t="s">
+      <c r="W6" s="89" t="s">
         <v>2094</v>
       </c>
       <c r="X6" s="85" t="s">
@@ -29652,36 +30600,36 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACEA719C-BCDA-4879-90DE-131AA5DAD230}">
-  <dimension ref="A1:X29"/>
+  <dimension ref="A1:AQ30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="98" t="s">
         <v>1884</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
-      <c r="V1" s="106"/>
-      <c r="W1" s="106"/>
-      <c r="X1" s="106"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="98"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
+      <c r="O1" s="98"/>
+      <c r="P1" s="98"/>
+      <c r="Q1" s="98"/>
+      <c r="R1" s="98"/>
+      <c r="S1" s="98"/>
+      <c r="T1" s="98"/>
+      <c r="U1" s="98"/>
+      <c r="V1" s="98"/>
+      <c r="W1" s="98"/>
+      <c r="X1" s="98"/>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -30669,7 +31617,7 @@
       </c>
       <c r="X16" s="9"/>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>15</v>
       </c>
@@ -30739,7 +31687,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>16</v>
       </c>
@@ -30803,7 +31751,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
         <v>17</v>
       </c>
@@ -30865,7 +31813,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>18</v>
       </c>
@@ -30923,7 +31871,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A21" s="9">
         <v>19</v>
       </c>
@@ -30981,7 +31929,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A22" s="9">
         <v>20</v>
       </c>
@@ -31039,7 +31987,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A23" s="9">
         <v>21</v>
       </c>
@@ -31097,7 +32045,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
         <v>22</v>
       </c>
@@ -31161,7 +32109,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A25" s="9">
         <v>23</v>
       </c>
@@ -31225,7 +32173,7 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
         <v>24</v>
       </c>
@@ -31289,7 +32237,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A27" s="9">
         <v>25</v>
       </c>
@@ -31353,7 +32301,7 @@
         <v>2055</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A28" s="9">
         <v>26</v>
       </c>
@@ -31419,31 +32367,148 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="9"/>
-      <c r="O29" s="9"/>
-      <c r="P29" s="9"/>
-      <c r="Q29" s="9"/>
-      <c r="R29" s="9"/>
-      <c r="S29" s="9"/>
-      <c r="T29" s="9"/>
-      <c r="U29" s="9"/>
-      <c r="V29" s="9"/>
-      <c r="W29" s="9"/>
-      <c r="X29" s="9"/>
+    <row r="29" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="A29" s="166">
+        <v>25</v>
+      </c>
+      <c r="B29" s="166" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C29" s="166" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D29" s="166" t="s">
+        <v>2310</v>
+      </c>
+      <c r="E29" s="166" t="s">
+        <v>2311</v>
+      </c>
+      <c r="F29" s="166" t="s">
+        <v>845</v>
+      </c>
+      <c r="G29" s="167">
+        <v>39724</v>
+      </c>
+      <c r="H29" s="166" t="s">
+        <v>2312</v>
+      </c>
+      <c r="I29" s="166" t="s">
+        <v>2313</v>
+      </c>
+      <c r="J29" s="166">
+        <v>7795682767</v>
+      </c>
+      <c r="K29" s="166">
+        <v>9632825418</v>
+      </c>
+      <c r="L29" s="168" t="s">
+        <v>2314</v>
+      </c>
+      <c r="M29" s="168" t="s">
+        <v>2315</v>
+      </c>
+      <c r="N29" s="166"/>
+      <c r="O29" s="166" t="s">
+        <v>91</v>
+      </c>
+      <c r="P29" s="166"/>
+      <c r="Q29" s="166">
+        <v>600</v>
+      </c>
+      <c r="R29" s="166">
+        <v>59</v>
+      </c>
+      <c r="S29" s="166">
+        <v>349</v>
+      </c>
+      <c r="T29" s="166"/>
+      <c r="U29" s="166"/>
+      <c r="V29" s="166"/>
+      <c r="W29" s="166" t="s">
+        <v>2316</v>
+      </c>
+      <c r="X29" s="166"/>
+      <c r="Y29" s="161"/>
+      <c r="Z29" s="161"/>
+      <c r="AA29" s="161"/>
+      <c r="AB29" s="161"/>
+      <c r="AC29" s="161"/>
+      <c r="AD29" s="161"/>
+      <c r="AE29" s="161"/>
+      <c r="AF29" s="161"/>
+      <c r="AG29" s="161"/>
+      <c r="AH29" s="161"/>
+      <c r="AI29" s="161"/>
+      <c r="AJ29" s="161"/>
+      <c r="AK29" s="161"/>
+      <c r="AL29" s="161"/>
+      <c r="AM29" s="161"/>
+      <c r="AN29" s="161"/>
+      <c r="AO29" s="161"/>
+      <c r="AP29" s="161"/>
+      <c r="AQ29" s="161"/>
+    </row>
+    <row r="30" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="A30" s="169">
+        <v>26</v>
+      </c>
+      <c r="B30" s="169" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C30" s="169" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D30" s="169" t="s">
+        <v>2317</v>
+      </c>
+      <c r="E30" s="169" t="s">
+        <v>2318</v>
+      </c>
+      <c r="F30" s="169" t="s">
+        <v>813</v>
+      </c>
+      <c r="G30" s="170">
+        <v>39831</v>
+      </c>
+      <c r="H30" s="169" t="s">
+        <v>2319</v>
+      </c>
+      <c r="I30" s="169" t="s">
+        <v>2320</v>
+      </c>
+      <c r="J30" s="169">
+        <v>9740485278</v>
+      </c>
+      <c r="K30" s="169">
+        <v>9632477672</v>
+      </c>
+      <c r="L30" s="171" t="s">
+        <v>2321</v>
+      </c>
+      <c r="M30" s="171" t="s">
+        <v>2322</v>
+      </c>
+      <c r="N30" s="169"/>
+      <c r="O30" s="169"/>
+      <c r="P30" s="169"/>
+      <c r="Q30" s="169">
+        <v>600</v>
+      </c>
+      <c r="R30" s="169">
+        <v>60</v>
+      </c>
+      <c r="S30" s="169">
+        <v>349</v>
+      </c>
+      <c r="T30" s="170"/>
+      <c r="U30" s="169"/>
+      <c r="V30" s="169"/>
+      <c r="W30" s="169" t="s">
+        <v>2323</v>
+      </c>
+      <c r="X30" s="172" t="s">
+        <v>2324</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -31473,6 +32538,7 @@
     <hyperlink ref="X26" r:id="rId21" xr:uid="{D3F45E9E-F06D-42EB-8877-1F9ACC4FC750}"/>
     <hyperlink ref="X27" r:id="rId22" xr:uid="{B5D1B0F3-F56D-4470-9658-F2585E405FB8}"/>
     <hyperlink ref="X28" r:id="rId23" xr:uid="{DEABA608-C0C1-4E46-89FD-27D4937B7554}"/>
+    <hyperlink ref="X30" r:id="rId24" xr:uid="{00000000-0004-0000-0200-000021000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
